--- a/CONCILIACAO_COMPLETA_2024_2026.xlsx
+++ b/CONCILIACAO_COMPLETA_2024_2026.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONCILIAÇÃO MENSAL" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DETALHAMENTO" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="RESUMO COMPRADOR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DIVERGÊNCIAS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ENTRADAS MENSAL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PAGAMENTOS REALIZADOS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="FLUXO DE CAIXA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DETALHE ENTRADAS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="RESUMO COMPRADOR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DIVERGÊNCIAS" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,11 +62,34 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="004472C4"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FF0000"/>
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -97,8 +122,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
         <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6DCE4"/>
+        <bgColor rgb="00D6DCE4"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,7 +171,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -146,14 +183,31 @@
     <xf numFmtId="4" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="12" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -555,7 +609,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CONCILIAÇÃO BANCÁRIA - EXCLUSIVA SERVICE LTDA</t>
+          <t>ENTRADAS - PAGAMENTOS DOS COMPRADORES</t>
         </is>
       </c>
     </row>
@@ -569,7 +623,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>OBS: GRACIANA PEREIRA LOURENCO e MARIA PEREIRA DA SILVA pagam pelos mesmos lotes (consolidado)</t>
+          <t>OBS: GRACIANA PEREIRA e MARIA PEREIRA pagam pelos mesmos lotes (consolidado)</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2769,7 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>NUNCA PAGOU - R$ 0,00 - TOTAL INADIMPLENTE</t>
+          <t>NUNCA PAGOU - TOTAL INADIMPLENTE</t>
         </is>
       </c>
     </row>
@@ -2728,6 +2782,2335 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E84"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>SAÍDAS - PAGAMENTOS REALIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Total de saídas no período: R$ 159,793.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>DESTINATÁRIO/DESCRIÇÃO</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>VALOR (R$)</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>CATEGORIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>15/07/2024</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>8800</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>16/07/2024</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>21/07/2024</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>23/07/2024</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>BOLETO</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>IBIUNA</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>PREFEITURA/CARTÓRIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>23/07/2024</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>BOLETO</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>IBIUNA</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>PREFEITURA/CARTÓRIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>23/07/2024</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>BOLETO</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>IBIUNA</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>135.32</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>PREFEITURA/CARTÓRIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>23/07/2024</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>BOLETO</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>IBIUNA</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>PREFEITURA/CARTÓRIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>23/07/2024</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>BOLETO</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>IBIUNA</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>135.32</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>PREFEITURA/CARTÓRIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>24/07/2024</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Cesar Augusto de Oliveira</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>PIX P/ TERCEIROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>24/07/2024</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>MARINA LEITE AGOSTINHO SOCIEDADE</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>HONORÁRIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>06/08/2024</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>594.16</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>11/08/2024</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>13/08/2024</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>18/08/2024</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>25/08/2024</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>27/08/2024</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Marina Leite Agostinho Sociedade Individual de</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>HONORÁRIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>16/09/2024</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2024</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>ALISSON RAFAEL MORAES</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>PIX P/ TERCEIROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>10/10/2024</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Editora Ibiuna Ltda</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>190</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>PREFEITURA/CARTÓRIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>13/10/2024</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>WANIA CRISTINA DA CRUZ</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>138.69</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>PIX P/ TERCEIROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>13/10/2024</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>7635.95</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>23/10/2024</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Dionisio Grangeiro Neto</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>4950</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>TOPÓGRAFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>30/10/2024</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>24/11/2024</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>06/01/2025</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>07/01/2025</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>12/01/2025</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>17/01/2025</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Dionisio Grangeiro Neto</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>11900</v>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>TOPÓGRAFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>23/02/2025</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>3250</v>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>16/03/2025</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>3250</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>17/03/2025</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>DIONISIO GRANGEIRO NETO</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>11900</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>TOPÓGRAFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>12/04/2025</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>22/04/2025</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Gicele Capovilla Alves</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>PIX P/ TERCEIROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>15/06/2025</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>10251.42</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>JOSE OGIER JACOM NETO</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>1750</v>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>PIX P/ TERCEIROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>12/10/2025</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>06/11/2025</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>SIMONE BASTOS GOMES</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>196.43</v>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>PIX P/ TERCEIROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Simone Bastos Gomes</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>1750</v>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>PIX P/ TERCEIROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>13/12/2025</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>BOLETO</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>GEAZI ASSIS DE SOUZA OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>PREFEITURA/CARTÓRIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="n">
+        <v>9600</v>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL GERAL SAÍDAS</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="n">
+        <v>159793.45</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>RESUMO POR CATEGORIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="inlineStr">
+        <is>
+          <t>CATEGORIA</t>
+        </is>
+      </c>
+      <c r="B56" s="21" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="inlineStr">
+        <is>
+          <t>TOTAL (R$)</t>
+        </is>
+      </c>
+      <c r="D56" s="21" t="inlineStr">
+        <is>
+          <t>% DO TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>HONORÁRIOS</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D57" s="23" t="n">
+        <v>0.0938711818287921</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>TOPÓGRAFO</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" s="22" t="n">
+        <v>28750</v>
+      </c>
+      <c r="D58" s="23" t="n">
+        <v>0.1799197651718515</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>PREFEITURA/CARTÓRIO</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C59" s="22" t="n">
+        <v>791.4400000000001</v>
+      </c>
+      <c r="D59" s="23" t="n">
+        <v>0.004952893876438615</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>PIX P/ TERCEIROS</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C60" s="22" t="n">
+        <v>10670.48</v>
+      </c>
+      <c r="D60" s="23" t="n">
+        <v>0.06677670455203263</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C61" s="22" t="n">
+        <v>104581.53</v>
+      </c>
+      <c r="D61" s="23" t="n">
+        <v>0.6544794545708851</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t>SAÍDAS POR MÊS (excl. Aplicação RDB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="21" t="inlineStr">
+        <is>
+          <t>MÊS</t>
+        </is>
+      </c>
+      <c r="B64" s="21" t="inlineStr">
+        <is>
+          <t>PIX/BOLETOS</t>
+        </is>
+      </c>
+      <c r="C64" s="21" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="D64" s="21" t="inlineStr">
+        <is>
+          <t>TOTAL MÊS</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>JUL/24</t>
+        </is>
+      </c>
+      <c r="B65" s="24" t="n">
+        <v>9405.940000000001</v>
+      </c>
+      <c r="C65" s="25" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D65" s="22" t="n">
+        <v>20205.94</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>AGO/24</t>
+        </is>
+      </c>
+      <c r="B66" s="24" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C66" s="25" t="n">
+        <v>9594.16</v>
+      </c>
+      <c r="D66" s="22" t="n">
+        <v>18594.16</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>SET/24</t>
+        </is>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D67" s="22" t="n">
+        <v>6035.36</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>OUT/24</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="n">
+        <v>5278.69</v>
+      </c>
+      <c r="C68" s="25" t="n">
+        <v>8135.95</v>
+      </c>
+      <c r="D68" s="22" t="n">
+        <v>13414.64</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>NOV/24</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="25" t="n">
+        <v>7250</v>
+      </c>
+      <c r="D69" s="22" t="n">
+        <v>7250</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>JAN/25</t>
+        </is>
+      </c>
+      <c r="B70" s="24" t="n">
+        <v>11900</v>
+      </c>
+      <c r="C70" s="25" t="n">
+        <v>8500</v>
+      </c>
+      <c r="D70" s="22" t="n">
+        <v>20400</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>FEV/25</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="25" t="n">
+        <v>4750</v>
+      </c>
+      <c r="D71" s="22" t="n">
+        <v>4750</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>MAR/25</t>
+        </is>
+      </c>
+      <c r="B72" s="24" t="n">
+        <v>11900</v>
+      </c>
+      <c r="C72" s="25" t="n">
+        <v>3250</v>
+      </c>
+      <c r="D72" s="22" t="n">
+        <v>15150</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>ABR/25</t>
+        </is>
+      </c>
+      <c r="B73" s="24" t="n">
+        <v>3800</v>
+      </c>
+      <c r="C73" s="25" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D73" s="22" t="n">
+        <v>6550</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>JUN/25</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="25" t="n">
+        <v>10251.42</v>
+      </c>
+      <c r="D74" s="22" t="n">
+        <v>10251.42</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>JUL/25</t>
+        </is>
+      </c>
+      <c r="B75" s="24" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C75" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="22" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>AGO/25</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="25" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D76" s="22" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>SET/25</t>
+        </is>
+      </c>
+      <c r="B77" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D77" s="22" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>OUT/25</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="25" t="n">
+        <v>6500</v>
+      </c>
+      <c r="D78" s="22" t="n">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>NOV/25</t>
+        </is>
+      </c>
+      <c r="B79" s="24" t="n">
+        <v>1946.43</v>
+      </c>
+      <c r="C79" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="22" t="n">
+        <v>1946.43</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>DEZ/25</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="25" t="n">
+        <v>5500</v>
+      </c>
+      <c r="D80" s="22" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>FEV/26</t>
+        </is>
+      </c>
+      <c r="B81" s="24" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="C81" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="22" t="n">
+        <v>195.5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>MAR/26</t>
+        </is>
+      </c>
+      <c r="B82" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="25" t="n">
+        <v>9600</v>
+      </c>
+      <c r="D82" s="22" t="n">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>ABR/26</t>
+        </is>
+      </c>
+      <c r="B83" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="25" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D83" s="22" t="n">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>MAI/26</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="25" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D84" s="22" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FLUXO DE CAIXA MENSAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>Saldo inicial: R$ 0,10 | Saldo final: R$ 1.841,29</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>MÊS</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>ENTRADAS</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>SAÍDAS (Pgtos)</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>SAÍDAS (RDB)</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>TOTAL SAÍDAS</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>SALDO MENSAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>JUL/24</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C5" s="24" t="n">
+        <v>9405.940000000001</v>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>10800</v>
+      </c>
+      <c r="E5" s="22" t="n">
+        <v>20205.94</v>
+      </c>
+      <c r="F5" s="29" t="n">
+        <v>-10205.94</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>AGO/24</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>9594.16</v>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>18594.16</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>-9094.16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SET/24</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C7" s="24" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E7" s="22" t="n">
+        <v>6035.36</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>3464.64</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>OUT/24</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C8" s="24" t="n">
+        <v>5278.69</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>8135.95</v>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>13414.64</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>-4914.639999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>NOV/24</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="n">
+        <v>8250</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>7250</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DEZ/24</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>JAN/25</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C11" s="24" t="n">
+        <v>11900</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>8500</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>20400</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>-17400</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>FEV/25</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="n">
+        <v>4250</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>4750</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>4750</v>
+      </c>
+      <c r="F12" s="29" t="n">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>MAR/25</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>11900</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>3250</v>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>15150</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>-11150</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ABR/25</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>3800</v>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E14" s="22" t="n">
+        <v>6550</v>
+      </c>
+      <c r="F14" s="29" t="n">
+        <v>-2050</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MAI/25</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>JUN/25</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>10251.42</v>
+      </c>
+      <c r="E16" s="22" t="n">
+        <v>10251.42</v>
+      </c>
+      <c r="F16" s="29" t="n">
+        <v>-6251.42</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>JUL/25</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C17" s="24" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="22" t="n">
+        <v>1750</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>AGO/25</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="n">
+        <v>3250</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="25" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E18" s="22" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F18" s="29" t="n">
+        <v>-2750</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SET/25</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="n">
+        <v>3250</v>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E19" s="22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>OUT/25</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="n">
+        <v>4250</v>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="25" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E20" s="22" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F20" s="29" t="n">
+        <v>-2250</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>NOV/25</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C21" s="24" t="n">
+        <v>1946.43</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>1946.43</v>
+      </c>
+      <c r="F21" s="30" t="n">
+        <v>2053.57</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>DEZ/25</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="n">
+        <v>3250</v>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="25" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F22" s="29" t="n">
+        <v>-2250</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>JAN/26</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="30" t="n">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>FEV/26</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="n">
+        <v>3750</v>
+      </c>
+      <c r="C24" s="24" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="F24" s="30" t="n">
+        <v>3554.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>MAR/26</t>
+        </is>
+      </c>
+      <c r="B25" s="28" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>9600</v>
+      </c>
+      <c r="E25" s="22" t="n">
+        <v>9600</v>
+      </c>
+      <c r="F25" s="29" t="n">
+        <v>-6600</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>ABR/26</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="25" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E26" s="22" t="n">
+        <v>2700</v>
+      </c>
+      <c r="F26" s="29" t="n">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>MAI/26</t>
+        </is>
+      </c>
+      <c r="B27" s="28" t="n">
+        <v>2530</v>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="25" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E27" s="22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F27" s="30" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>JUN/26</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="30" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n">
+        <v>112780</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>55211.92000000001</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>104581.53</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>159793.45</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>-47013.45</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2746,32 +5129,32 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TODAS AS TRANSFERÊNCIAS RECEBIDAS - DETALHAMENTO</t>
+          <t>DETALHAMENTO - TODAS AS TRANSFERÊNCIAS RECEBIDAS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>COMPRADOR</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>NOME NO EXTRATO</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>VALOR (R$)</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t>LOTE(S)</t>
         </is>
@@ -2793,7 +5176,7 @@
           <t>HERALDO DE ALMEIDA SOUZA</t>
         </is>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -2818,7 +5201,7 @@
           <t>JEFFERSON LUIZ DOS SANTOS ALVES</t>
         </is>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -2843,7 +5226,7 @@
           <t>Felipe Santos de Oliveira</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -2868,7 +5251,7 @@
           <t>VINICIUS NICOLAS DE ALMEIDA TA</t>
         </is>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -2893,7 +5276,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -2918,7 +5301,7 @@
           <t>Tatiane Pereira dos Santos</t>
         </is>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -2943,7 +5326,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -2968,7 +5351,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -2993,7 +5376,7 @@
           <t>RAPHAEL PINHEIRO</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -3018,7 +5401,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -3043,7 +5426,7 @@
           <t>Israel ferreira do Amaral</t>
         </is>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -3068,7 +5451,7 @@
           <t>GRACIANA PEREIRA LOURENCO</t>
         </is>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -3093,7 +5476,7 @@
           <t>LEANDRO DA SILVA</t>
         </is>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -3118,7 +5501,7 @@
           <t>LUCIANA SILVA CABRAL LOBATO</t>
         </is>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -3143,7 +5526,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -3168,7 +5551,7 @@
           <t>JOSE NAILTON LOPES DA SILVA</t>
         </is>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -3193,7 +5576,7 @@
           <t>Felipe Santos de Oliveira</t>
         </is>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -3218,7 +5601,7 @@
           <t>VINICIUS NICOLAS DE ALMEIDA TA</t>
         </is>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -3243,7 +5626,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -3268,7 +5651,7 @@
           <t>MARIA PEREIRA DA SILVA</t>
         </is>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -3293,7 +5676,7 @@
           <t>MARIA PEREIRA DA SILVA</t>
         </is>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -3318,7 +5701,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="D25" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -3343,7 +5726,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -3368,7 +5751,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -3393,7 +5776,7 @@
           <t>RAPHAEL PINHEIRO</t>
         </is>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -3418,7 +5801,7 @@
           <t>Tatiane Pereira dos Santos</t>
         </is>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -3443,7 +5826,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -3468,7 +5851,7 @@
           <t>Heraldo de Almeida Souza</t>
         </is>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="D31" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3493,7 +5876,7 @@
           <t>LEANDRO DA SILVA</t>
         </is>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -3518,7 +5901,7 @@
           <t>Eduardo Nunes Lobato</t>
         </is>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D33" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -3543,7 +5926,7 @@
           <t>HERALDO DE ALMEIDA SOUZA 18006238871 -</t>
         </is>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -3568,7 +5951,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="D35" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3593,7 +5976,7 @@
           <t>HERALDO DE ALMEIDA SOUZA 18006238871 -</t>
         </is>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D36" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -3618,7 +6001,7 @@
           <t>Felipe Santos de Oliveira</t>
         </is>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3643,7 +6026,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -3668,7 +6051,7 @@
           <t>Tatiane Pereira dos Santos</t>
         </is>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -3693,7 +6076,7 @@
           <t>LEANDRO DA SILVA</t>
         </is>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="D40" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -3718,7 +6101,7 @@
           <t>MARIA PEREIRA DA SILVA</t>
         </is>
       </c>
-      <c r="D41" s="16" t="n">
+      <c r="D41" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -3743,7 +6126,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="D42" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -3768,7 +6151,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D43" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -3793,7 +6176,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="D44" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -3818,7 +6201,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -3843,7 +6226,7 @@
           <t>RAPHAEL PINHEIRO</t>
         </is>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="D46" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -3868,7 +6251,7 @@
           <t>ANDERSON DE JESUS SILVA PAIVA</t>
         </is>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -3893,7 +6276,7 @@
           <t>VINICIUS NICOLAS DE ALMEIDA TA</t>
         </is>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="D48" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -3918,7 +6301,7 @@
           <t>SENARIA DO NASCIMENTO MALTA</t>
         </is>
       </c>
-      <c r="D49" s="16" t="n">
+      <c r="D49" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -3943,7 +6326,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="D50" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -3968,7 +6351,7 @@
           <t>Eduardo Nunes Lobato</t>
         </is>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="D51" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -3993,7 +6376,7 @@
           <t>RAPHAEL PINHEIRO</t>
         </is>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="D52" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -4018,7 +6401,7 @@
           <t>ANDERSON DE JESUS SILVA PAIVA</t>
         </is>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="D53" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -4043,7 +6426,7 @@
           <t>JEFFERSON LUIZ DOS SANTOS ALVES</t>
         </is>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="D54" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -4068,7 +6451,7 @@
           <t>HERALDO DE ALMEIDA SOUZA 18006238871 -</t>
         </is>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="D55" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -4093,7 +6476,7 @@
           <t>ANDERSON DE JESUS SILVA PAIVA</t>
         </is>
       </c>
-      <c r="D56" s="16" t="n">
+      <c r="D56" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -4118,7 +6501,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D57" s="16" t="n">
+      <c r="D57" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -4143,7 +6526,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D58" s="16" t="n">
+      <c r="D58" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -4168,7 +6551,7 @@
           <t>ANDERSON J S PAIVA</t>
         </is>
       </c>
-      <c r="D59" s="16" t="n">
+      <c r="D59" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -4193,7 +6576,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D60" s="16" t="n">
+      <c r="D60" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -4218,7 +6601,7 @@
           <t>Tatiane Pereira dos Santos</t>
         </is>
       </c>
-      <c r="D61" s="16" t="n">
+      <c r="D61" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -4243,7 +6626,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D62" s="16" t="n">
+      <c r="D62" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -4268,7 +6651,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D63" s="16" t="n">
+      <c r="D63" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -4293,7 +6676,7 @@
           <t>RAPHAEL PINHEIRO</t>
         </is>
       </c>
-      <c r="D64" s="16" t="n">
+      <c r="D64" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -4318,7 +6701,7 @@
           <t>Felipe Santos de Oliveira</t>
         </is>
       </c>
-      <c r="D65" s="16" t="n">
+      <c r="D65" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -4343,7 +6726,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D66" s="16" t="n">
+      <c r="D66" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -4368,7 +6751,7 @@
           <t>Eduardo Nunes Lobato</t>
         </is>
       </c>
-      <c r="D67" s="16" t="n">
+      <c r="D67" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -4393,7 +6776,7 @@
           <t>JEFFERSON LUIZ DOS SANTOS ALVES</t>
         </is>
       </c>
-      <c r="D68" s="16" t="n">
+      <c r="D68" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -4418,7 +6801,7 @@
           <t>VINICIUS NICOLAS DE ALMEIDA TA</t>
         </is>
       </c>
-      <c r="D69" s="16" t="n">
+      <c r="D69" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -4443,7 +6826,7 @@
           <t>HERALDO DE ALMEIDA SOUZA 18006238871 -</t>
         </is>
       </c>
-      <c r="D70" s="16" t="n">
+      <c r="D70" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -4468,7 +6851,7 @@
           <t>HERALDO DE ALMEIDA SOUZA 18006238871 -</t>
         </is>
       </c>
-      <c r="D71" s="16" t="n">
+      <c r="D71" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -4493,7 +6876,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D72" s="16" t="n">
+      <c r="D72" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -4518,7 +6901,7 @@
           <t>Tatiane Pereira dos Santos</t>
         </is>
       </c>
-      <c r="D73" s="16" t="n">
+      <c r="D73" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -4543,7 +6926,7 @@
           <t>LEANDRO DA SILVA</t>
         </is>
       </c>
-      <c r="D74" s="16" t="n">
+      <c r="D74" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -4568,7 +6951,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D75" s="16" t="n">
+      <c r="D75" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -4593,7 +6976,7 @@
           <t>ANDERSON J S PAIVA</t>
         </is>
       </c>
-      <c r="D76" s="16" t="n">
+      <c r="D76" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -4618,7 +7001,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D77" s="16" t="n">
+      <c r="D77" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -4643,7 +7026,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D78" s="16" t="n">
+      <c r="D78" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -4668,7 +7051,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D79" s="16" t="n">
+      <c r="D79" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -4693,7 +7076,7 @@
           <t>Eduardo Nunes Lobato</t>
         </is>
       </c>
-      <c r="D80" s="16" t="n">
+      <c r="D80" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -4718,7 +7101,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D81" s="16" t="n">
+      <c r="D81" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -4743,7 +7126,7 @@
           <t>JOSE NAILTON LOPES DA SILVA</t>
         </is>
       </c>
-      <c r="D82" s="16" t="n">
+      <c r="D82" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -4768,7 +7151,7 @@
           <t>RAPHAEL PINHEIRO</t>
         </is>
       </c>
-      <c r="D83" s="16" t="n">
+      <c r="D83" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -4793,7 +7176,7 @@
           <t>HERALDO DE ALMEIDA SOUZA 18006238871 -</t>
         </is>
       </c>
-      <c r="D84" s="16" t="n">
+      <c r="D84" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E84" s="4" t="inlineStr">
@@ -4818,7 +7201,7 @@
           <t>JEFFERSON LUIZ DOS SANTOS ALVES</t>
         </is>
       </c>
-      <c r="D85" s="16" t="n">
+      <c r="D85" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -4843,7 +7226,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D86" s="16" t="n">
+      <c r="D86" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -4868,7 +7251,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D87" s="16" t="n">
+      <c r="D87" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -4893,7 +7276,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D88" s="16" t="n">
+      <c r="D88" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -4918,7 +7301,7 @@
           <t>Kathleen Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D89" s="16" t="n">
+      <c r="D89" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -4943,7 +7326,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D90" s="16" t="n">
+      <c r="D90" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -4968,7 +7351,7 @@
           <t>Eduardo Nunes Lobato</t>
         </is>
       </c>
-      <c r="D91" s="16" t="n">
+      <c r="D91" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -4993,7 +7376,7 @@
           <t>VINICIUS NICOLAS DE ALMEIDA TA</t>
         </is>
       </c>
-      <c r="D92" s="16" t="n">
+      <c r="D92" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -5018,7 +7401,7 @@
           <t>SENARIA DO NASCIMENTO MALTA</t>
         </is>
       </c>
-      <c r="D93" s="16" t="n">
+      <c r="D93" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -5043,7 +7426,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D94" s="16" t="n">
+      <c r="D94" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -5068,7 +7451,7 @@
           <t>ANDERSON DE JESUS SILVA PAIVA</t>
         </is>
       </c>
-      <c r="D95" s="16" t="n">
+      <c r="D95" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -5093,7 +7476,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D96" s="16" t="n">
+      <c r="D96" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -5118,7 +7501,7 @@
           <t>VINICIUS NICOLAS DE ALMEIDA TA</t>
         </is>
       </c>
-      <c r="D97" s="16" t="n">
+      <c r="D97" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -5143,7 +7526,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D98" s="16" t="n">
+      <c r="D98" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -5168,7 +7551,7 @@
           <t>LEANDRO DA SILVA</t>
         </is>
       </c>
-      <c r="D99" s="16" t="n">
+      <c r="D99" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -5193,7 +7576,7 @@
           <t>Israel ferreira do Amaral</t>
         </is>
       </c>
-      <c r="D100" s="16" t="n">
+      <c r="D100" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -5218,7 +7601,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D101" s="16" t="n">
+      <c r="D101" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -5243,7 +7626,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D102" s="16" t="n">
+      <c r="D102" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -5268,7 +7651,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D103" s="16" t="n">
+      <c r="D103" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -5293,7 +7676,7 @@
           <t>HERALDO DE ALMEIDA SOUZA 18006238871 -</t>
         </is>
       </c>
-      <c r="D104" s="16" t="n">
+      <c r="D104" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -5318,7 +7701,7 @@
           <t>Eduardo Nunes Lobato</t>
         </is>
       </c>
-      <c r="D105" s="16" t="n">
+      <c r="D105" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -5343,7 +7726,7 @@
           <t>HERALDO DE ALMEIDA SOUZA</t>
         </is>
       </c>
-      <c r="D106" s="16" t="n">
+      <c r="D106" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -5368,7 +7751,7 @@
           <t>VINICIUS NICOLAS DE ALMEIDA TA</t>
         </is>
       </c>
-      <c r="D107" s="16" t="n">
+      <c r="D107" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -5393,7 +7776,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D108" s="16" t="n">
+      <c r="D108" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -5418,7 +7801,7 @@
           <t>ANDERSON J S PAIVA</t>
         </is>
       </c>
-      <c r="D109" s="16" t="n">
+      <c r="D109" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -5443,7 +7826,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D110" s="16" t="n">
+      <c r="D110" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -5468,7 +7851,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D111" s="16" t="n">
+      <c r="D111" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -5493,7 +7876,7 @@
           <t>LEANDRO DA SILVA</t>
         </is>
       </c>
-      <c r="D112" s="16" t="n">
+      <c r="D112" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -5518,7 +7901,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D113" s="16" t="n">
+      <c r="D113" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -5543,7 +7926,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D114" s="16" t="n">
+      <c r="D114" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -5568,7 +7951,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D115" s="16" t="n">
+      <c r="D115" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -5593,7 +7976,7 @@
           <t>SENARIA DO NASCIMENTO MALTA</t>
         </is>
       </c>
-      <c r="D116" s="16" t="n">
+      <c r="D116" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -5618,7 +8001,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D117" s="16" t="n">
+      <c r="D117" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -5643,7 +8026,7 @@
           <t>GILBERTO MUNIN JUNIOR</t>
         </is>
       </c>
-      <c r="D118" s="16" t="n">
+      <c r="D118" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -5668,7 +8051,7 @@
           <t>HERALDO DE ALMEIDA SOUZA</t>
         </is>
       </c>
-      <c r="D119" s="16" t="n">
+      <c r="D119" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -5693,7 +8076,7 @@
           <t>Eduardo Nunes Lobato</t>
         </is>
       </c>
-      <c r="D120" s="16" t="n">
+      <c r="D120" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E120" s="4" t="inlineStr">
@@ -5718,7 +8101,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D121" s="16" t="n">
+      <c r="D121" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -5743,7 +8126,7 @@
           <t>LEANDRO DA SILVA</t>
         </is>
       </c>
-      <c r="D122" s="16" t="n">
+      <c r="D122" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -5768,7 +8151,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D123" s="16" t="n">
+      <c r="D123" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -5793,7 +8176,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D124" s="16" t="n">
+      <c r="D124" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E124" s="4" t="inlineStr">
@@ -5818,7 +8201,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D125" s="16" t="n">
+      <c r="D125" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -5843,7 +8226,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D126" s="16" t="n">
+      <c r="D126" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -5868,7 +8251,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D127" s="16" t="n">
+      <c r="D127" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -5893,7 +8276,7 @@
           <t>MARIA PEREIRA DA SILVA LIMA</t>
         </is>
       </c>
-      <c r="D128" s="16" t="n">
+      <c r="D128" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -5918,7 +8301,7 @@
           <t>Eduardo Nunes Lobato</t>
         </is>
       </c>
-      <c r="D129" s="16" t="n">
+      <c r="D129" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -5943,7 +8326,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D130" s="16" t="n">
+      <c r="D130" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -5968,7 +8351,7 @@
           <t>VINICIUS NICOLAS DE ALMEIDA TA</t>
         </is>
       </c>
-      <c r="D131" s="16" t="n">
+      <c r="D131" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -5993,7 +8376,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D132" s="16" t="n">
+      <c r="D132" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E132" s="4" t="inlineStr">
@@ -6018,7 +8401,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D133" s="16" t="n">
+      <c r="D133" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -6043,7 +8426,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D134" s="16" t="n">
+      <c r="D134" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -6068,7 +8451,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D135" s="16" t="n">
+      <c r="D135" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -6093,7 +8476,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D136" s="16" t="n">
+      <c r="D136" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -6118,7 +8501,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D137" s="16" t="n">
+      <c r="D137" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -6143,7 +8526,7 @@
           <t>LEANDRO DA SILVA</t>
         </is>
       </c>
-      <c r="D138" s="16" t="n">
+      <c r="D138" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E138" s="4" t="inlineStr">
@@ -6168,7 +8551,7 @@
           <t>ANDERSON DE JESUS SILVA PAIVA</t>
         </is>
       </c>
-      <c r="D139" s="16" t="n">
+      <c r="D139" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -6193,7 +8576,7 @@
           <t>MARIA PEREIRA DA SILVA</t>
         </is>
       </c>
-      <c r="D140" s="16" t="n">
+      <c r="D140" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E140" s="4" t="inlineStr">
@@ -6218,7 +8601,7 @@
           <t>JEFFERSON LUIZ DOS SANTOS ALVES</t>
         </is>
       </c>
-      <c r="D141" s="16" t="n">
+      <c r="D141" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -6243,7 +8626,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D142" s="16" t="n">
+      <c r="D142" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E142" s="4" t="inlineStr">
@@ -6268,7 +8651,7 @@
           <t>ANDERSON DE JESUS SILVA PAIVA</t>
         </is>
       </c>
-      <c r="D143" s="16" t="n">
+      <c r="D143" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -6293,7 +8676,7 @@
           <t>Gilberto Munin Junior</t>
         </is>
       </c>
-      <c r="D144" s="16" t="n">
+      <c r="D144" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E144" s="4" t="inlineStr">
@@ -6318,7 +8701,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D145" s="16" t="n">
+      <c r="D145" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -6343,7 +8726,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D146" s="16" t="n">
+      <c r="D146" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E146" s="4" t="inlineStr">
@@ -6368,7 +8751,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D147" s="16" t="n">
+      <c r="D147" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -6393,7 +8776,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D148" s="16" t="n">
+      <c r="D148" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E148" s="4" t="inlineStr">
@@ -6418,7 +8801,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D149" s="16" t="n">
+      <c r="D149" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -6443,7 +8826,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D150" s="16" t="n">
+      <c r="D150" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E150" s="4" t="inlineStr">
@@ -6468,7 +8851,7 @@
           <t>LEANDRO DA SILVA</t>
         </is>
       </c>
-      <c r="D151" s="16" t="n">
+      <c r="D151" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -6493,7 +8876,7 @@
           <t>MARIA PEREIRA DA SILVA</t>
         </is>
       </c>
-      <c r="D152" s="16" t="n">
+      <c r="D152" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E152" s="4" t="inlineStr">
@@ -6518,7 +8901,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D153" s="16" t="n">
+      <c r="D153" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -6543,7 +8926,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D154" s="16" t="n">
+      <c r="D154" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E154" s="4" t="inlineStr">
@@ -6568,7 +8951,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D155" s="16" t="n">
+      <c r="D155" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -6593,7 +8976,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D156" s="16" t="n">
+      <c r="D156" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E156" s="4" t="inlineStr">
@@ -6618,7 +9001,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D157" s="16" t="n">
+      <c r="D157" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -6643,7 +9026,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D158" s="16" t="n">
+      <c r="D158" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E158" s="4" t="inlineStr">
@@ -6668,7 +9051,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D159" s="16" t="n">
+      <c r="D159" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -6693,7 +9076,7 @@
           <t>LEANDRO DA SILVA</t>
         </is>
       </c>
-      <c r="D160" s="16" t="n">
+      <c r="D160" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E160" s="4" t="inlineStr">
@@ -6718,7 +9101,7 @@
           <t>MARIA PEREIRA DA SILVA</t>
         </is>
       </c>
-      <c r="D161" s="16" t="n">
+      <c r="D161" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E161" s="4" t="inlineStr">
@@ -6743,7 +9126,7 @@
           <t>JEFFERSON LUIZ DOS SANTOS ALVES</t>
         </is>
       </c>
-      <c r="D162" s="16" t="n">
+      <c r="D162" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E162" s="4" t="inlineStr">
@@ -6768,7 +9151,7 @@
           <t>VINICIUS NICOLAS DE ALMEIDA TA</t>
         </is>
       </c>
-      <c r="D163" s="16" t="n">
+      <c r="D163" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E163" s="4" t="inlineStr">
@@ -6793,7 +9176,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D164" s="16" t="n">
+      <c r="D164" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E164" s="4" t="inlineStr">
@@ -6818,7 +9201,7 @@
           <t>Eduardo Nunes Lobato</t>
         </is>
       </c>
-      <c r="D165" s="16" t="n">
+      <c r="D165" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E165" s="4" t="inlineStr">
@@ -6843,7 +9226,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D166" s="16" t="n">
+      <c r="D166" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E166" s="4" t="inlineStr">
@@ -6868,7 +9251,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D167" s="16" t="n">
+      <c r="D167" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E167" s="4" t="inlineStr">
@@ -6893,7 +9276,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D168" s="16" t="n">
+      <c r="D168" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E168" s="4" t="inlineStr">
@@ -6918,7 +9301,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D169" s="16" t="n">
+      <c r="D169" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E169" s="4" t="inlineStr">
@@ -6943,7 +9326,7 @@
           <t>MARIA PEREIRA DA SILVA</t>
         </is>
       </c>
-      <c r="D170" s="16" t="n">
+      <c r="D170" s="18" t="n">
         <v>750</v>
       </c>
       <c r="E170" s="4" t="inlineStr">
@@ -6968,7 +9351,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D171" s="16" t="n">
+      <c r="D171" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E171" s="4" t="inlineStr">
@@ -6993,7 +9376,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D172" s="16" t="n">
+      <c r="D172" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E172" s="4" t="inlineStr">
@@ -7018,7 +9401,7 @@
           <t>LEANDRO DA SILVA</t>
         </is>
       </c>
-      <c r="D173" s="16" t="n">
+      <c r="D173" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E173" s="4" t="inlineStr">
@@ -7043,7 +9426,7 @@
           <t>Vinícius Nicolas De Almeida Tardeo</t>
         </is>
       </c>
-      <c r="D174" s="16" t="n">
+      <c r="D174" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E174" s="4" t="inlineStr">
@@ -7068,7 +9451,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D175" s="16" t="n">
+      <c r="D175" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E175" s="4" t="inlineStr">
@@ -7093,7 +9476,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D176" s="16" t="n">
+      <c r="D176" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E176" s="4" t="inlineStr">
@@ -7118,7 +9501,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D177" s="16" t="n">
+      <c r="D177" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E177" s="4" t="inlineStr">
@@ -7143,7 +9526,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D178" s="16" t="n">
+      <c r="D178" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E178" s="4" t="inlineStr">
@@ -7168,7 +9551,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D179" s="16" t="n">
+      <c r="D179" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E179" s="4" t="inlineStr">
@@ -7193,7 +9576,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D180" s="16" t="n">
+      <c r="D180" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E180" s="4" t="inlineStr">
@@ -7218,7 +9601,7 @@
           <t>MARIA PEREIRA DA SILVA</t>
         </is>
       </c>
-      <c r="D181" s="16" t="n">
+      <c r="D181" s="18" t="n">
         <v>750</v>
       </c>
       <c r="E181" s="4" t="inlineStr">
@@ -7243,7 +9626,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D182" s="16" t="n">
+      <c r="D182" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E182" s="4" t="inlineStr">
@@ -7268,7 +9651,7 @@
           <t>LEANDRO DA SILVA</t>
         </is>
       </c>
-      <c r="D183" s="16" t="n">
+      <c r="D183" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E183" s="4" t="inlineStr">
@@ -7293,7 +9676,7 @@
           <t>JEFFERSON LUIZ DOS SANTOS ALVES</t>
         </is>
       </c>
-      <c r="D184" s="16" t="n">
+      <c r="D184" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E184" s="4" t="inlineStr">
@@ -7318,7 +9701,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D185" s="16" t="n">
+      <c r="D185" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E185" s="4" t="inlineStr">
@@ -7343,7 +9726,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D186" s="16" t="n">
+      <c r="D186" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E186" s="4" t="inlineStr">
@@ -7368,7 +9751,7 @@
           <t>ANDERSON J S PAIVA</t>
         </is>
       </c>
-      <c r="D187" s="16" t="n">
+      <c r="D187" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E187" s="4" t="inlineStr">
@@ -7393,7 +9776,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D188" s="16" t="n">
+      <c r="D188" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E188" s="4" t="inlineStr">
@@ -7418,7 +9801,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D189" s="16" t="n">
+      <c r="D189" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E189" s="4" t="inlineStr">
@@ -7443,7 +9826,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D190" s="16" t="n">
+      <c r="D190" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E190" s="4" t="inlineStr">
@@ -7468,7 +9851,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D191" s="16" t="n">
+      <c r="D191" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E191" s="4" t="inlineStr">
@@ -7493,7 +9876,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D192" s="16" t="n">
+      <c r="D192" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E192" s="4" t="inlineStr">
@@ -7518,7 +9901,7 @@
           <t>MARIA PEREIRA DA SILVA</t>
         </is>
       </c>
-      <c r="D193" s="16" t="n">
+      <c r="D193" s="18" t="n">
         <v>750</v>
       </c>
       <c r="E193" s="4" t="inlineStr">
@@ -7543,7 +9926,7 @@
           <t>JEFFERSON LUIZ DOS SANTOS ALVES</t>
         </is>
       </c>
-      <c r="D194" s="16" t="n">
+      <c r="D194" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E194" s="4" t="inlineStr">
@@ -7568,7 +9951,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D195" s="16" t="n">
+      <c r="D195" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E195" s="4" t="inlineStr">
@@ -7593,7 +9976,7 @@
           <t>Vinícius Nicolas De Almeida Tardeo</t>
         </is>
       </c>
-      <c r="D196" s="16" t="n">
+      <c r="D196" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E196" s="4" t="inlineStr">
@@ -7618,7 +10001,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D197" s="16" t="n">
+      <c r="D197" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E197" s="4" t="inlineStr">
@@ -7643,7 +10026,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D198" s="16" t="n">
+      <c r="D198" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E198" s="4" t="inlineStr">
@@ -7668,7 +10051,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D199" s="16" t="n">
+      <c r="D199" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E199" s="4" t="inlineStr">
@@ -7693,7 +10076,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D200" s="16" t="n">
+      <c r="D200" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E200" s="4" t="inlineStr">
@@ -7718,7 +10101,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D201" s="16" t="n">
+      <c r="D201" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E201" s="4" t="inlineStr">
@@ -7743,7 +10126,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D202" s="16" t="n">
+      <c r="D202" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E202" s="4" t="inlineStr">
@@ -7768,7 +10151,7 @@
           <t>MARIA PEREIRA DA SILVA</t>
         </is>
       </c>
-      <c r="D203" s="16" t="n">
+      <c r="D203" s="18" t="n">
         <v>750</v>
       </c>
       <c r="E203" s="4" t="inlineStr">
@@ -7793,7 +10176,7 @@
           <t>Gilberto Munin Junior</t>
         </is>
       </c>
-      <c r="D204" s="16" t="n">
+      <c r="D204" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E204" s="4" t="inlineStr">
@@ -7818,7 +10201,7 @@
           <t>JEFFERSON LUIZ DOS SANTOS ALVES</t>
         </is>
       </c>
-      <c r="D205" s="16" t="n">
+      <c r="D205" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E205" s="4" t="inlineStr">
@@ -7843,7 +10226,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D206" s="16" t="n">
+      <c r="D206" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E206" s="4" t="inlineStr">
@@ -7868,7 +10251,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D207" s="16" t="n">
+      <c r="D207" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E207" s="4" t="inlineStr">
@@ -7893,7 +10276,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D208" s="16" t="n">
+      <c r="D208" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E208" s="4" t="inlineStr">
@@ -7918,7 +10301,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D209" s="16" t="n">
+      <c r="D209" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E209" s="4" t="inlineStr">
@@ -7943,7 +10326,7 @@
           <t>MARIA PEREIRA DA SILVA</t>
         </is>
       </c>
-      <c r="D210" s="16" t="n">
+      <c r="D210" s="18" t="n">
         <v>750</v>
       </c>
       <c r="E210" s="4" t="inlineStr">
@@ -7968,7 +10351,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D211" s="16" t="n">
+      <c r="D211" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E211" s="4" t="inlineStr">
@@ -7993,7 +10376,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D212" s="16" t="n">
+      <c r="D212" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E212" s="4" t="inlineStr">
@@ -8018,7 +10401,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D213" s="16" t="n">
+      <c r="D213" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E213" s="4" t="inlineStr">
@@ -8043,7 +10426,7 @@
           <t>JEFFERSON LUIZ DOS SANTOS ALVES</t>
         </is>
       </c>
-      <c r="D214" s="16" t="n">
+      <c r="D214" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E214" s="4" t="inlineStr">
@@ -8068,7 +10451,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D215" s="16" t="n">
+      <c r="D215" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E215" s="4" t="inlineStr">
@@ -8093,7 +10476,7 @@
           <t>Gilberto Munin Junior</t>
         </is>
       </c>
-      <c r="D216" s="16" t="n">
+      <c r="D216" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E216" s="4" t="inlineStr">
@@ -8118,7 +10501,7 @@
           <t>VINICIUS NICOLAS DE ALMEIDA TA</t>
         </is>
       </c>
-      <c r="D217" s="16" t="n">
+      <c r="D217" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E217" s="4" t="inlineStr">
@@ -8143,7 +10526,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D218" s="16" t="n">
+      <c r="D218" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E218" s="4" t="inlineStr">
@@ -8168,7 +10551,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D219" s="16" t="n">
+      <c r="D219" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E219" s="4" t="inlineStr">
@@ -8193,7 +10576,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D220" s="16" t="n">
+      <c r="D220" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E220" s="4" t="inlineStr">
@@ -8218,7 +10601,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D221" s="16" t="n">
+      <c r="D221" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E221" s="4" t="inlineStr">
@@ -8243,7 +10626,7 @@
           <t>MARIA PEREIRA DA SILVA</t>
         </is>
       </c>
-      <c r="D222" s="16" t="n">
+      <c r="D222" s="18" t="n">
         <v>750</v>
       </c>
       <c r="E222" s="4" t="inlineStr">
@@ -8268,7 +10651,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D223" s="16" t="n">
+      <c r="D223" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E223" s="4" t="inlineStr">
@@ -8293,7 +10676,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D224" s="16" t="n">
+      <c r="D224" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E224" s="4" t="inlineStr">
@@ -8318,7 +10701,7 @@
           <t>JEFFERSON LUIZ DOS SANTOS ALVES</t>
         </is>
       </c>
-      <c r="D225" s="16" t="n">
+      <c r="D225" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E225" s="4" t="inlineStr">
@@ -8343,7 +10726,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D226" s="16" t="n">
+      <c r="D226" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E226" s="4" t="inlineStr">
@@ -8368,7 +10751,7 @@
           <t>VINICIUS NICOLAS DE ALMEIDA TA</t>
         </is>
       </c>
-      <c r="D227" s="16" t="n">
+      <c r="D227" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E227" s="4" t="inlineStr">
@@ -8393,7 +10776,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D228" s="16" t="n">
+      <c r="D228" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E228" s="4" t="inlineStr">
@@ -8418,7 +10801,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D229" s="16" t="n">
+      <c r="D229" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E229" s="4" t="inlineStr">
@@ -8443,7 +10826,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D230" s="16" t="n">
+      <c r="D230" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E230" s="4" t="inlineStr">
@@ -8468,7 +10851,7 @@
           <t>MARIA PEREIRA DA SILVA</t>
         </is>
       </c>
-      <c r="D231" s="16" t="n">
+      <c r="D231" s="18" t="n">
         <v>750</v>
       </c>
       <c r="E231" s="4" t="inlineStr">
@@ -8493,7 +10876,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D232" s="16" t="n">
+      <c r="D232" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E232" s="4" t="inlineStr">
@@ -8518,7 +10901,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D233" s="16" t="n">
+      <c r="D233" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E233" s="4" t="inlineStr">
@@ -8543,7 +10926,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D234" s="16" t="n">
+      <c r="D234" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E234" s="4" t="inlineStr">
@@ -8568,7 +10951,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D235" s="16" t="n">
+      <c r="D235" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E235" s="4" t="inlineStr">
@@ -8593,7 +10976,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D236" s="16" t="n">
+      <c r="D236" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E236" s="4" t="inlineStr">
@@ -8618,7 +11001,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D237" s="16" t="n">
+      <c r="D237" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E237" s="4" t="inlineStr">
@@ -8643,7 +11026,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D238" s="16" t="n">
+      <c r="D238" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E238" s="4" t="inlineStr">
@@ -8668,7 +11051,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D239" s="16" t="n">
+      <c r="D239" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E239" s="4" t="inlineStr">
@@ -8693,7 +11076,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D240" s="16" t="n">
+      <c r="D240" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E240" s="4" t="inlineStr">
@@ -8718,7 +11101,7 @@
           <t>MARIA PEREIRA DA SILVA</t>
         </is>
       </c>
-      <c r="D241" s="16" t="n">
+      <c r="D241" s="18" t="n">
         <v>750</v>
       </c>
       <c r="E241" s="4" t="inlineStr">
@@ -8743,7 +11126,7 @@
           <t>Gilberto Munin Junior</t>
         </is>
       </c>
-      <c r="D242" s="16" t="n">
+      <c r="D242" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="E242" s="4" t="inlineStr">
@@ -8768,7 +11151,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D243" s="16" t="n">
+      <c r="D243" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E243" s="4" t="inlineStr">
@@ -8793,7 +11176,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D244" s="16" t="n">
+      <c r="D244" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E244" s="4" t="inlineStr">
@@ -8818,7 +11201,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D245" s="16" t="n">
+      <c r="D245" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E245" s="4" t="inlineStr">
@@ -8843,7 +11226,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D246" s="16" t="n">
+      <c r="D246" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E246" s="4" t="inlineStr">
@@ -8868,7 +11251,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D247" s="16" t="n">
+      <c r="D247" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E247" s="4" t="inlineStr">
@@ -8893,7 +11276,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D248" s="16" t="n">
+      <c r="D248" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E248" s="4" t="inlineStr">
@@ -8918,7 +11301,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D249" s="16" t="n">
+      <c r="D249" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E249" s="4" t="inlineStr">
@@ -8943,7 +11326,7 @@
           <t>MARIA PEREIRA DA SILVA</t>
         </is>
       </c>
-      <c r="D250" s="16" t="n">
+      <c r="D250" s="18" t="n">
         <v>750</v>
       </c>
       <c r="E250" s="4" t="inlineStr">
@@ -8968,7 +11351,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D251" s="16" t="n">
+      <c r="D251" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E251" s="4" t="inlineStr">
@@ -8993,7 +11376,7 @@
           <t>JEFFERSON LUIZ SANTOS ALVES</t>
         </is>
       </c>
-      <c r="D252" s="16" t="n">
+      <c r="D252" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E252" s="4" t="inlineStr">
@@ -9018,7 +11401,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D253" s="16" t="n">
+      <c r="D253" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E253" s="4" t="inlineStr">
@@ -9043,7 +11426,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D254" s="16" t="n">
+      <c r="D254" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E254" s="4" t="inlineStr">
@@ -9068,7 +11451,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D255" s="16" t="n">
+      <c r="D255" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E255" s="4" t="inlineStr">
@@ -9093,7 +11476,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D256" s="16" t="n">
+      <c r="D256" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E256" s="4" t="inlineStr">
@@ -9118,7 +11501,7 @@
           <t>MARIA PEREIRA DA SILVA LIMA</t>
         </is>
       </c>
-      <c r="D257" s="16" t="n">
+      <c r="D257" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E257" s="4" t="inlineStr">
@@ -9143,7 +11526,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D258" s="16" t="n">
+      <c r="D258" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E258" s="4" t="inlineStr">
@@ -9168,7 +11551,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="D259" s="16" t="n">
+      <c r="D259" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E259" s="4" t="inlineStr">
@@ -9193,7 +11576,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D260" s="16" t="n">
+      <c r="D260" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E260" s="4" t="inlineStr">
@@ -9218,7 +11601,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D261" s="16" t="n">
+      <c r="D261" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E261" s="4" t="inlineStr">
@@ -9243,7 +11626,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D262" s="16" t="n">
+      <c r="D262" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E262" s="4" t="inlineStr">
@@ -9268,7 +11651,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D263" s="16" t="n">
+      <c r="D263" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E263" s="4" t="inlineStr">
@@ -9293,7 +11676,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D264" s="16" t="n">
+      <c r="D264" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E264" s="4" t="inlineStr">
@@ -9318,7 +11701,7 @@
           <t>GRACIANA PEREIRA LOURENCO</t>
         </is>
       </c>
-      <c r="D265" s="16" t="n">
+      <c r="D265" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E265" s="4" t="inlineStr">
@@ -9343,7 +11726,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="D266" s="16" t="n">
+      <c r="D266" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E266" s="4" t="inlineStr">
@@ -9368,7 +11751,7 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="D267" s="16" t="n">
+      <c r="D267" s="18" t="n">
         <v>30</v>
       </c>
       <c r="E267" s="4" t="inlineStr">
@@ -9393,7 +11776,7 @@
           <t>VINICIUS NICOLAS DE ALMEIDA TA</t>
         </is>
       </c>
-      <c r="D268" s="16" t="n">
+      <c r="D268" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E268" s="4" t="inlineStr">
@@ -9418,7 +11801,7 @@
           <t>Kevin Daniel Santos Figueiredo</t>
         </is>
       </c>
-      <c r="D269" s="16" t="n">
+      <c r="D269" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E269" s="4" t="inlineStr">
@@ -9443,7 +11826,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="D270" s="16" t="n">
+      <c r="D270" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E270" s="4" t="inlineStr">
@@ -9468,7 +11851,7 @@
           <t>Eduardo Rodrigues da Silva</t>
         </is>
       </c>
-      <c r="D271" s="16" t="n">
+      <c r="D271" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E271" s="4" t="inlineStr">
@@ -9493,7 +11876,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="D272" s="16" t="n">
+      <c r="D272" s="18" t="n">
         <v>250</v>
       </c>
       <c r="E272" s="4" t="inlineStr">
@@ -9507,7 +11890,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9534,42 +11917,42 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>COMPRADOR</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>LOTE(S)</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>TOTAL PAGO</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>QTD PAGTOS</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t>1º PAGTO</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>ÚLTIMO PAGTO</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="21" t="inlineStr">
         <is>
           <t>VALOR LOTE(S)</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t>% PAGO</t>
         </is>
@@ -9586,7 +11969,7 @@
           <t>1, 2, 20, 29, 30</t>
         </is>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="22" t="n">
         <v>15250</v>
       </c>
       <c r="D4" s="4" t="n">
@@ -9602,10 +11985,10 @@
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="G4" s="16" t="n">
+      <c r="G4" s="18" t="n">
         <v>60000</v>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="32" t="n">
         <v>0.2541666666666667</v>
       </c>
     </row>
@@ -9620,7 +12003,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="22" t="n">
         <v>4500</v>
       </c>
       <c r="D5" s="4" t="n">
@@ -9636,10 +12019,10 @@
           <t>23/03/2026</t>
         </is>
       </c>
-      <c r="G5" s="16" t="n">
+      <c r="G5" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="32" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -9654,7 +12037,7 @@
           <t>4, 5</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="22" t="n">
         <v>5000</v>
       </c>
       <c r="D6" s="4" t="n">
@@ -9670,10 +12053,10 @@
           <t>25/11/2024</t>
         </is>
       </c>
-      <c r="G6" s="16" t="n">
+      <c r="G6" s="18" t="n">
         <v>24000</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="33" t="n">
         <v>0.2083333333333333</v>
       </c>
     </row>
@@ -9688,7 +12071,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="22" t="n">
         <v>7000</v>
       </c>
       <c r="D7" s="4" t="n">
@@ -9704,10 +12087,10 @@
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="34" t="n">
         <v>0.5833333333333334</v>
       </c>
     </row>
@@ -9722,7 +12105,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="22" t="n">
         <v>2750</v>
       </c>
       <c r="D8" s="4" t="n">
@@ -9738,10 +12121,10 @@
           <t>10/09/2025</t>
         </is>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="33" t="n">
         <v>0.2291666666666667</v>
       </c>
     </row>
@@ -9756,7 +12139,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="22" t="n">
         <v>7000</v>
       </c>
       <c r="D9" s="4" t="n">
@@ -9772,10 +12155,10 @@
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="34" t="n">
         <v>0.5833333333333334</v>
       </c>
     </row>
@@ -9790,7 +12173,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="22" t="n">
         <v>2500</v>
       </c>
       <c r="D10" s="4" t="n">
@@ -9806,10 +12189,10 @@
           <t>09/11/2024</t>
         </is>
       </c>
-      <c r="G10" s="16" t="n">
+      <c r="G10" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="33" t="n">
         <v>0.2083333333333333</v>
       </c>
     </row>
@@ -9824,7 +12207,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="22" t="n">
         <v>5000</v>
       </c>
       <c r="D11" s="4" t="n">
@@ -9840,10 +12223,10 @@
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H11" s="18" t="n">
+      <c r="H11" s="32" t="n">
         <v>0.4166666666666667</v>
       </c>
     </row>
@@ -9858,7 +12241,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="22" t="n">
         <v>500</v>
       </c>
       <c r="D12" s="4" t="n">
@@ -9874,10 +12257,10 @@
           <t>15/07/2024</t>
         </is>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="33" t="n">
         <v>0.04166666666666666</v>
       </c>
     </row>
@@ -9892,7 +12275,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="22" t="n">
         <v>3500</v>
       </c>
       <c r="D13" s="4" t="n">
@@ -9908,10 +12291,10 @@
           <t>06/07/2025</t>
         </is>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H13" s="32" t="n">
         <v>0.2916666666666667</v>
       </c>
     </row>
@@ -9926,7 +12309,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="22" t="n">
         <v>2000</v>
       </c>
       <c r="D14" s="4" t="n">
@@ -9942,10 +12325,10 @@
           <t>19/10/2024</t>
         </is>
       </c>
-      <c r="G14" s="16" t="n">
+      <c r="G14" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H14" s="19" t="n">
+      <c r="H14" s="33" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
@@ -9960,7 +12343,7 @@
           <t>17, 21</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="22" t="n">
         <v>5250</v>
       </c>
       <c r="D15" s="4" t="n">
@@ -9976,10 +12359,10 @@
           <t>06/03/2025</t>
         </is>
       </c>
-      <c r="G15" s="16" t="n">
+      <c r="G15" s="18" t="n">
         <v>24000</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H15" s="33" t="n">
         <v>0.21875</v>
       </c>
     </row>
@@ -9994,7 +12377,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="22" t="n">
         <v>750</v>
       </c>
       <c r="D16" s="4" t="n">
@@ -10010,10 +12393,10 @@
           <t>10/01/2025</t>
         </is>
       </c>
-      <c r="G16" s="16" t="n">
+      <c r="G16" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H16" s="19" t="n">
+      <c r="H16" s="33" t="n">
         <v>0.0625</v>
       </c>
     </row>
@@ -10028,7 +12411,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="22" t="n">
         <v>5780</v>
       </c>
       <c r="D17" s="4" t="n">
@@ -10044,10 +12427,10 @@
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="G17" s="16" t="n">
+      <c r="G17" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H17" s="18" t="n">
+      <c r="H17" s="32" t="n">
         <v>0.4816666666666667</v>
       </c>
     </row>
@@ -10062,7 +12445,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="22" t="n">
         <v>7500</v>
       </c>
       <c r="D18" s="4" t="n">
@@ -10078,10 +12461,10 @@
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="G18" s="16" t="n">
+      <c r="G18" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H18" s="20" t="n">
+      <c r="H18" s="34" t="n">
         <v>0.625</v>
       </c>
     </row>
@@ -10096,7 +12479,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C19" s="22" t="n">
         <v>1250</v>
       </c>
       <c r="D19" s="4" t="n">
@@ -10112,10 +12495,10 @@
           <t>20/02/2025</t>
         </is>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H19" s="19" t="n">
+      <c r="H19" s="33" t="n">
         <v>0.1041666666666667</v>
       </c>
     </row>
@@ -10130,7 +12513,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C20" s="22" t="n">
         <v>4750</v>
       </c>
       <c r="D20" s="4" t="n">
@@ -10146,10 +12529,10 @@
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H20" s="18" t="n">
+      <c r="H20" s="32" t="n">
         <v>0.3958333333333333</v>
       </c>
     </row>
@@ -10164,7 +12547,7 @@
           <t>23, 24</t>
         </is>
       </c>
-      <c r="C21" s="17" t="n">
+      <c r="C21" s="22" t="n">
         <v>14500</v>
       </c>
       <c r="D21" s="4" t="n">
@@ -10180,10 +12563,10 @@
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="G21" s="18" t="n">
         <v>24000</v>
       </c>
-      <c r="H21" s="20" t="n">
+      <c r="H21" s="34" t="n">
         <v>0.6041666666666666</v>
       </c>
     </row>
@@ -10198,7 +12581,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C22" s="17" t="n">
+      <c r="C22" s="22" t="n">
         <v>4000</v>
       </c>
       <c r="D22" s="4" t="n">
@@ -10214,10 +12597,10 @@
           <t>10/08/2025</t>
         </is>
       </c>
-      <c r="G22" s="16" t="n">
+      <c r="G22" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H22" s="18" t="n">
+      <c r="H22" s="32" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -10232,7 +12615,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C23" s="17" t="n">
+      <c r="C23" s="22" t="n">
         <v>7500</v>
       </c>
       <c r="D23" s="4" t="n">
@@ -10248,10 +12631,10 @@
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="G23" s="16" t="n">
+      <c r="G23" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H23" s="20" t="n">
+      <c r="H23" s="34" t="n">
         <v>0.625</v>
       </c>
     </row>
@@ -10266,7 +12649,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C24" s="17" t="n">
+      <c r="C24" s="22" t="n">
         <v>1500</v>
       </c>
       <c r="D24" s="4" t="n">
@@ -10282,10 +12665,10 @@
           <t>21/11/2024</t>
         </is>
       </c>
-      <c r="G24" s="16" t="n">
+      <c r="G24" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="H24" s="19" t="n">
+      <c r="H24" s="33" t="n">
         <v>0.125</v>
       </c>
     </row>
@@ -10300,7 +12683,7 @@
           <t>28, 29</t>
         </is>
       </c>
-      <c r="C25" s="17" t="n">
+      <c r="C25" s="22" t="n">
         <v>5000</v>
       </c>
       <c r="D25" s="4" t="n">
@@ -10316,10 +12699,10 @@
           <t>12/02/2026</t>
         </is>
       </c>
-      <c r="G25" s="16" t="n">
+      <c r="G25" s="18" t="n">
         <v>24000</v>
       </c>
-      <c r="H25" s="19" t="n">
+      <c r="H25" s="33" t="n">
         <v>0.2083333333333333</v>
       </c>
     </row>
@@ -10328,7 +12711,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10338,29 +12721,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>PONTOS DE ATENÇÃO E DIVERGÊNCIAS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>COMPRADOR</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
@@ -10374,12 +12757,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Pagou R$ 500 em MAI/26. Paga pelos mesmos lotes de MARIA PEREIRA (informado pela gestora). Valores consolidados.</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>Pagou R$ 500 em MAI/26. Paga mesmos lotes de MARIA PEREIRA (consolidado).</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>ATENÇÃO</t>
         </is>
       </c>
     </row>
@@ -10391,10 +12774,10 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Pagou R$ 30,00 em 26/05/2026 (parcela habitual: R$ 250). Verificar se pagamento parcial ou ajuste.</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
+          <t>Pagou R$ 30 em 26/05/2026 (parcela habitual R$ 250). Verificar.</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -10408,12 +12791,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ABR/26: pagou R$ 500 (habitual R$ 750). Um dos lotes ficou em aberto. MAI e JUN/26: sem pagamento direto (Graciana pagou R$500 em MAI).</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>ABR/26: pagou R$ 500 (habitual R$ 750). MAI e JUN/26: sem pagamento direto.</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>ATENÇÃO</t>
         </is>
       </c>
     </row>
@@ -10425,10 +12808,10 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Pagamentos irregulares (R$ 1.000 esporádicos). Sem pagamentos desde FEV/26.</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
+          <t>Pagamentos irregulares (R$ 1.000 esporádicos). Sem pagto desde FEV/26.</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -10442,10 +12825,10 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Parcela reduzida de R$500 para R$250 a partir de AGO/25. Sem pagto FEV/26. Pagou MAR/26 e parou.</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
+          <t>Parcela reduzida. Sem pagto FEV/26. Pagou MAR/26 e parou.</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -10462,7 +12845,7 @@
           <t>Sem pagamento em ABR/26 e JUN/26.</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -10476,10 +12859,10 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Pagamentos irregulares. Meses sem pagar. Último: JUN/26.</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
+          <t>Pagamentos irregulares. Meses sem pagar.</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -10493,12 +12876,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Pagamento consistente R$ 500/mês (2 lotes). Sem pagamento JUN/26 (extrato até 11/06).</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>ATENÇÃO</t>
+          <t>Consistente R$ 500/mês. Sem JUN/26 (extrato até 11/06).</t>
+        </is>
+      </c>
+      <c r="C11" s="37" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -10510,10 +12893,10 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>INADIMPLENTE. Parou de pagar após NOV/2024.</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
+          <t>INADIMPLENTE. Parou após NOV/2024.</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -10527,10 +12910,10 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>INADIMPLENTE TOTAL. Lote 6 - Nunca pagou.</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
+          <t>Lote 6 - NUNCA PAGOU.</t>
+        </is>
+      </c>
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -10544,10 +12927,10 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>INADIMPLENTE. Parou de pagar após OUT/2024.</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
+          <t>INADIMPLENTE. Parou após OUT/2024.</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -10561,12 +12944,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Pagamentos irregulares. Último pagamento SET/25.</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>ATENÇÃO</t>
+          <t>Pagamentos irregulares. Último SET/25.</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>INADIMPLENTE</t>
         </is>
       </c>
     </row>
@@ -10578,10 +12961,10 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>INADIMPLENTE. Parou de pagar após MAR/2025.</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
+          <t>INADIMPLENTE. Parou após MAR/2025.</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -10595,10 +12978,10 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>INADIMPLENTE. Último pagamento JUN/2025.</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
+          <t>INADIMPLENTE. Último pagto JUN/2025.</t>
+        </is>
+      </c>
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -10612,12 +12995,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>INADIMPLENTE. Pagou apenas JUL/2024 (R$500). Eduardo Nunes Lobato paga pelo mesmo lote.</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>INADIMPLENTE</t>
+          <t>Pagou apenas JUL/24. Eduardo N. Lobato paga pelo mesmo lote.</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="inlineStr">
+        <is>
+          <t>ATENÇÃO</t>
         </is>
       </c>
     </row>

--- a/CONCILIACAO_COMPLETA_2024_2026.xlsx
+++ b/CONCILIACAO_COMPLETA_2024_2026.xlsx
@@ -135,14 +135,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="00D6DCE4"/>
+        <bgColor rgb="00D6DCE4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6DCE4"/>
-        <bgColor rgb="00D6DCE4"/>
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
   </fills>
@@ -164,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -187,6 +187,11 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -207,7 +212,7 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -216,7 +221,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="13" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -816,13 +820,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>0</v>
@@ -840,64 +844,64 @@
         <v>0</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="S6" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="T6" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="X6" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="Y6" s="6" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="Z6" s="6" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="AA6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>3050</v>
+        <v>3812.5</v>
       </c>
       <c r="AC6" s="9" t="n">
         <v>12000</v>
       </c>
       <c r="AD6" s="10" t="n">
-        <v>8950</v>
+        <v>8187.5</v>
       </c>
       <c r="AE6" s="11" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.3177083333333333</v>
       </c>
     </row>
     <row r="7">
@@ -915,13 +919,13 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0</v>
@@ -939,64 +943,64 @@
         <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="T7" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="X7" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="Y7" s="6" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="Z7" s="6" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="AA7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" s="8" t="n">
-        <v>3050</v>
+        <v>3812.5</v>
       </c>
       <c r="AC7" s="9" t="n">
         <v>12000</v>
       </c>
       <c r="AD7" s="10" t="n">
-        <v>8950</v>
+        <v>8187.5</v>
       </c>
       <c r="AE7" s="11" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.3177083333333333</v>
       </c>
     </row>
     <row r="8">
@@ -1987,89 +1991,91 @@
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="7" t="n">
+      <c r="D18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AB18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="AC18" s="9" t="n">
-        <v>12000</v>
-      </c>
-      <c r="AD18" s="10" t="n">
-        <v>12000</v>
-      </c>
-      <c r="AE18" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -2078,93 +2084,95 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>TASSIA VIEIRA DOS SANTOS</t>
+          <t>WANIA CRISTINA DA CRUZ</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="7" t="n">
+      <c r="D19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AB19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="AC19" s="9" t="n">
-        <v>12000</v>
-      </c>
-      <c r="AD19" s="10" t="n">
-        <v>12000</v>
-      </c>
-      <c r="AE19" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -2173,97 +2181,95 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>ALISSON RAFAEL MORAES</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>ROBSON SABINO</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="7" t="n">
+          <t>WANIA CRISTINA DA CRUZ</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="n">
         <v>0</v>
       </c>
       <c r="AC20" s="9" t="n">
-        <v>12000</v>
-      </c>
-      <c r="AD20" s="10" t="n">
-        <v>12000</v>
-      </c>
-      <c r="AE20" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -2578,13 +2584,13 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>0</v>
@@ -2602,64 +2608,64 @@
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="T24" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="X24" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="Y24" s="6" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="Z24" s="6" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="AA24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB24" s="8" t="n">
-        <v>3050</v>
+        <v>3812.5</v>
       </c>
       <c r="AC24" s="9" t="n">
         <v>12000</v>
       </c>
       <c r="AD24" s="10" t="n">
-        <v>8950</v>
+        <v>8187.5</v>
       </c>
       <c r="AE24" s="11" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.3177083333333333</v>
       </c>
     </row>
     <row r="25">
@@ -3267,7 +3273,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>0</v>
@@ -3279,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>0</v>
@@ -3339,16 +3345,16 @@
         <v>0</v>
       </c>
       <c r="AB31" s="8" t="n">
-        <v>4000</v>
+        <v>3250</v>
       </c>
       <c r="AC31" s="9" t="n">
         <v>12000</v>
       </c>
       <c r="AD31" s="10" t="n">
-        <v>8000</v>
+        <v>8750</v>
       </c>
       <c r="AE31" s="11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2708333333333333</v>
       </c>
     </row>
     <row r="32">
@@ -3357,28 +3363,28 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>MARIA PEREIRA DA SILVA LIMA</t>
+          <t>GILBERTO MUNIN JUNIOR</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>GILBERTO MUNIN JUNIOR</t>
+          <t>JOSE NAILTON LOPES DA SILVA</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>300</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="7" t="n">
-        <v>0</v>
+      <c r="H32" s="6" t="n">
+        <v>500</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>0</v>
@@ -3389,65 +3395,65 @@
       <c r="K32" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="L32" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="M32" s="6" t="n">
-        <v>200</v>
+      <c r="L32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>700</v>
-      </c>
-      <c r="O32" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v>150</v>
+        <v>500</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="S32" s="6" t="n">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="T32" s="6" t="n">
-        <v>650</v>
-      </c>
-      <c r="U32" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="V32" s="6" t="n">
-        <v>150</v>
+        <v>500</v>
+      </c>
+      <c r="U32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>650</v>
-      </c>
-      <c r="X32" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="Y32" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z32" s="6" t="n">
-        <v>100</v>
+        <v>500</v>
+      </c>
+      <c r="X32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="AA32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB32" s="8" t="n">
-        <v>5550</v>
+        <v>3250</v>
       </c>
       <c r="AC32" s="9" t="n">
         <v>12000</v>
       </c>
       <c r="AD32" s="10" t="n">
-        <v>6450</v>
-      </c>
-      <c r="AE32" s="13" t="n">
-        <v>0.4625</v>
+        <v>8750</v>
+      </c>
+      <c r="AE32" s="11" t="n">
+        <v>0.2708333333333333</v>
       </c>
     </row>
     <row r="33">
@@ -3461,13 +3467,13 @@
       </c>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>0</v>
@@ -3485,168 +3491,168 @@
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="R33" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="T33" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="U33" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="V33" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="W33" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="X33" s="6" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="Y33" s="6" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="Z33" s="6" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="AA33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB33" s="8" t="n">
-        <v>3050</v>
+        <v>3812.5</v>
       </c>
       <c r="AC33" s="9" t="n">
         <v>12000</v>
       </c>
       <c r="AD33" s="10" t="n">
-        <v>8950</v>
+        <v>8187.5</v>
       </c>
       <c r="AE33" s="11" t="n">
-        <v>0.2541666666666667</v>
+        <v>0.3177083333333333</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n"/>
-      <c r="C35" s="15" t="n"/>
-      <c r="D35" s="16" t="n">
+      <c r="B35" s="18" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="19" t="n">
         <v>10000</v>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="E35" s="19" t="n">
         <v>9500</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="F35" s="19" t="n">
         <v>9500</v>
       </c>
-      <c r="G35" s="16" t="n">
+      <c r="G35" s="19" t="n">
         <v>8500</v>
       </c>
-      <c r="H35" s="16" t="n">
+      <c r="H35" s="19" t="n">
         <v>8250</v>
       </c>
-      <c r="I35" s="16" t="n">
+      <c r="I35" s="19" t="n">
         <v>6000</v>
       </c>
-      <c r="J35" s="16" t="n">
+      <c r="J35" s="19" t="n">
         <v>3000</v>
       </c>
-      <c r="K35" s="16" t="n">
+      <c r="K35" s="19" t="n">
         <v>4250</v>
       </c>
-      <c r="L35" s="16" t="n">
+      <c r="L35" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="M35" s="16" t="n">
+      <c r="M35" s="19" t="n">
         <v>4500</v>
       </c>
-      <c r="N35" s="16" t="n">
+      <c r="N35" s="19" t="n">
         <v>4500</v>
       </c>
-      <c r="O35" s="16" t="n">
+      <c r="O35" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="P35" s="16" t="n">
+      <c r="P35" s="19" t="n">
         <v>3500</v>
       </c>
-      <c r="Q35" s="16" t="n">
+      <c r="Q35" s="19" t="n">
         <v>3250</v>
       </c>
-      <c r="R35" s="16" t="n">
+      <c r="R35" s="19" t="n">
         <v>3250</v>
       </c>
-      <c r="S35" s="16" t="n">
+      <c r="S35" s="19" t="n">
         <v>4250</v>
       </c>
-      <c r="T35" s="16" t="n">
+      <c r="T35" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="U35" s="16" t="n">
+      <c r="U35" s="19" t="n">
         <v>3250</v>
       </c>
-      <c r="V35" s="16" t="n">
+      <c r="V35" s="19" t="n">
         <v>2750</v>
       </c>
-      <c r="W35" s="16" t="n">
+      <c r="W35" s="19" t="n">
         <v>3750</v>
       </c>
-      <c r="X35" s="16" t="n">
+      <c r="X35" s="19" t="n">
         <v>3000</v>
       </c>
-      <c r="Y35" s="16" t="n">
+      <c r="Y35" s="19" t="n">
         <v>2000</v>
       </c>
-      <c r="Z35" s="16" t="n">
+      <c r="Z35" s="19" t="n">
         <v>2530</v>
       </c>
-      <c r="AA35" s="16" t="n">
+      <c r="AA35" s="19" t="n">
         <v>1250</v>
       </c>
-      <c r="AB35" s="17" t="n">
+      <c r="AB35" s="20" t="n">
         <v>112780</v>
       </c>
       <c r="AC35" s="8" t="n">
-        <v>336000</v>
-      </c>
-      <c r="AD35" s="18" t="n">
-        <v>223220</v>
-      </c>
-      <c r="AE35" s="19" t="n">
-        <v>0.3356547619047619</v>
+        <v>300000</v>
+      </c>
+      <c r="AD35" s="21" t="n">
+        <v>187220</v>
+      </c>
+      <c r="AE35" s="22" t="n">
+        <v>0.3759333333333333</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>Lotes excluídos:</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Lote 12 (Redistribuído) | Lote 14 (Wania) | Lote 15 (Tassia) | Lote 16 (Alisson/Robson) | Lote 25 (Poço - não vendido)</t>
+          <t>Lote 12 (Redistribuído) | Lotes 14, 15, 16 (Wania - zerados) | Lote 25 (Poço - não vendido)</t>
         </is>
       </c>
     </row>
@@ -3711,137 +3717,137 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>PAGADOR</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>LOTE(S)</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>JUL/24</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>AGO/24</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>SET/24</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>OUT/24</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>NOV/24</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="24" t="inlineStr">
         <is>
           <t>DEZ/24</t>
         </is>
       </c>
-      <c r="I4" s="21" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>JAN/25</t>
         </is>
       </c>
-      <c r="J4" s="21" t="inlineStr">
+      <c r="J4" s="24" t="inlineStr">
         <is>
           <t>FEV/25</t>
         </is>
       </c>
-      <c r="K4" s="21" t="inlineStr">
+      <c r="K4" s="24" t="inlineStr">
         <is>
           <t>MAR/25</t>
         </is>
       </c>
-      <c r="L4" s="21" t="inlineStr">
+      <c r="L4" s="24" t="inlineStr">
         <is>
           <t>ABR/25</t>
         </is>
       </c>
-      <c r="M4" s="21" t="inlineStr">
+      <c r="M4" s="24" t="inlineStr">
         <is>
           <t>MAI/25</t>
         </is>
       </c>
-      <c r="N4" s="21" t="inlineStr">
+      <c r="N4" s="24" t="inlineStr">
         <is>
           <t>JUN/25</t>
         </is>
       </c>
-      <c r="O4" s="21" t="inlineStr">
+      <c r="O4" s="24" t="inlineStr">
         <is>
           <t>JUL/25</t>
         </is>
       </c>
-      <c r="P4" s="21" t="inlineStr">
+      <c r="P4" s="24" t="inlineStr">
         <is>
           <t>AGO/25</t>
         </is>
       </c>
-      <c r="Q4" s="21" t="inlineStr">
+      <c r="Q4" s="24" t="inlineStr">
         <is>
           <t>SET/25</t>
         </is>
       </c>
-      <c r="R4" s="21" t="inlineStr">
+      <c r="R4" s="24" t="inlineStr">
         <is>
           <t>OUT/25</t>
         </is>
       </c>
-      <c r="S4" s="21" t="inlineStr">
+      <c r="S4" s="24" t="inlineStr">
         <is>
           <t>NOV/25</t>
         </is>
       </c>
-      <c r="T4" s="21" t="inlineStr">
+      <c r="T4" s="24" t="inlineStr">
         <is>
           <t>DEZ/25</t>
         </is>
       </c>
-      <c r="U4" s="21" t="inlineStr">
+      <c r="U4" s="24" t="inlineStr">
         <is>
           <t>JAN/26</t>
         </is>
       </c>
-      <c r="V4" s="21" t="inlineStr">
+      <c r="V4" s="24" t="inlineStr">
         <is>
           <t>FEV/26</t>
         </is>
       </c>
-      <c r="W4" s="21" t="inlineStr">
+      <c r="W4" s="24" t="inlineStr">
         <is>
           <t>MAR/26</t>
         </is>
       </c>
-      <c r="X4" s="21" t="inlineStr">
+      <c r="X4" s="24" t="inlineStr">
         <is>
           <t>ABR/26</t>
         </is>
       </c>
-      <c r="Y4" s="21" t="inlineStr">
+      <c r="Y4" s="24" t="inlineStr">
         <is>
           <t>MAI/26</t>
         </is>
       </c>
-      <c r="Z4" s="21" t="inlineStr">
+      <c r="Z4" s="24" t="inlineStr">
         <is>
           <t>JUN/26</t>
         </is>
       </c>
-      <c r="AA4" s="21" t="inlineStr">
+      <c r="AA4" s="24" t="inlineStr">
         <is>
           <t>TOTAL PAGO</t>
         </is>
@@ -3853,81 +3859,81 @@
           <t>GRACIANA PEREIRA LOURENCO</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>1, 2, 20, 29, 30</t>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="D5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="23" t="n">
+      <c r="D5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="26" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="Z5" s="23" t="n">
+      <c r="Z5" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA5" s="8" t="n">
@@ -3940,12 +3946,12 @@
           <t>MARIA PEREIRA DA SILVA LIMA</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>1, 2, 20, 29, 30</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="n">
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>1, 2, 20, 30</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
@@ -3954,19 +3960,19 @@
       <c r="E6" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="F6" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="23" t="n">
+      <c r="F6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="26" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="6" t="n">
@@ -4011,10 +4017,10 @@
       <c r="X6" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="Y6" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="23" t="n">
+      <c r="Y6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA6" s="8" t="n">
@@ -4027,7 +4033,7 @@
           <t>JEFFERSON LUIZ SANTOS ALVES</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -4035,40 +4041,40 @@
       <c r="C7" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="D7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="23" t="n">
+      <c r="D7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="26" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="G7" s="23" t="n">
+      <c r="G7" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="I7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="23" t="n">
+      <c r="I7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="26" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="M7" s="23" t="n">
+      <c r="M7" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="O7" s="23" t="n">
+      <c r="O7" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="6" t="n">
@@ -4086,22 +4092,22 @@
       <c r="T7" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="U7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="23" t="n">
+      <c r="U7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="26" t="n">
         <v>0</v>
       </c>
       <c r="W7" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="X7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="23" t="n">
+      <c r="X7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="8" t="n">
@@ -4114,7 +4120,7 @@
           <t>RAPHAEL PINHEIRO</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>4, 5</t>
         </is>
@@ -4134,61 +4140,61 @@
       <c r="G8" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="H8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="23" t="n">
+      <c r="H8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA8" s="8" t="n">
@@ -4201,7 +4207,7 @@
           <t>VANDICE EUZEBIO DOS SANTOS</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -4269,13 +4275,13 @@
       <c r="W9" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="X9" s="23" t="n">
+      <c r="X9" s="26" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="Z9" s="23" t="n">
+      <c r="Z9" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA9" s="8" t="n">
@@ -4288,15 +4294,15 @@
           <t>ANDERSON DE JESUS PAIVA</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="23" t="n">
+      <c r="C10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="26" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="6" t="n">
@@ -4308,7 +4314,7 @@
       <c r="G10" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="H10" s="23" t="n">
+      <c r="H10" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
@@ -4317,7 +4323,7 @@
       <c r="J10" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="K10" s="23" t="n">
+      <c r="K10" s="26" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
@@ -4326,43 +4332,43 @@
       <c r="M10" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="N10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="23" t="n">
+      <c r="N10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="26" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="R10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="23" t="n">
+      <c r="R10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA10" s="8" t="n">
@@ -4375,7 +4381,7 @@
           <t>EDUARDO RODRIGUES DA SILVA</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -4398,7 +4404,7 @@
       <c r="H11" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="I11" s="23" t="n">
+      <c r="I11" s="26" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
@@ -4434,7 +4440,7 @@
       <c r="T11" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="U11" s="23" t="n">
+      <c r="U11" s="26" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="6" t="n">
@@ -4462,7 +4468,7 @@
           <t>TATIANE PEREIRA DOS SANTOS</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -4482,61 +4488,61 @@
       <c r="G12" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="H12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="23" t="n">
+      <c r="H12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA12" s="8" t="n">
@@ -4549,24 +4555,24 @@
           <t>KEVIN DANIEL SANTOS FIGUEIREDO</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C13" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="23" t="n">
+      <c r="C13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="6" t="n">
@@ -4636,7 +4642,7 @@
           <t>LUCIANA SILVA CABRAL LOBATO</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -4644,73 +4650,73 @@
       <c r="C14" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="D14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="23" t="n">
+      <c r="D14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA14" s="8" t="n">
@@ -4723,12 +4729,12 @@
           <t>EDUARDO NUNES LOBATO</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="6" t="n">
@@ -4749,55 +4755,55 @@
       <c r="I15" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="J15" s="23" t="n">
+      <c r="J15" s="26" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="L15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="23" t="n">
+      <c r="L15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="26" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="P15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="23" t="n">
+      <c r="P15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA15" s="8" t="n">
@@ -4810,7 +4816,7 @@
           <t>FELIPE SANTOS DE OLIVEIRA</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -4827,64 +4833,64 @@
       <c r="F16" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="G16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="23" t="n">
+      <c r="G16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA16" s="8" t="n">
@@ -4897,7 +4903,7 @@
           <t>HERALDO DE ALMEIDA SOUZA</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>17, 21</t>
         </is>
@@ -4929,49 +4935,49 @@
       <c r="K17" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="L17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="23" t="n">
+      <c r="L17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA17" s="8" t="n">
@@ -4984,7 +4990,7 @@
           <t>ISRAEL FERREIRA DO AMARAL</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -4992,73 +4998,73 @@
       <c r="C18" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="D18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="23" t="n">
+      <c r="D18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="J18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="23" t="n">
+      <c r="J18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA18" s="8" t="n">
@@ -5071,12 +5077,12 @@
           <t>ANDREZA SANTANA DAMACENO</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="C19" s="23" t="n">
+      <c r="C19" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="6" t="n">
@@ -5091,10 +5097,10 @@
       <c r="G19" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="H19" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="23" t="n">
+      <c r="H19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="26" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
@@ -5139,13 +5145,13 @@
       <c r="W19" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="X19" s="23" t="n">
+      <c r="X19" s="26" t="n">
         <v>0</v>
       </c>
       <c r="Y19" s="6" t="n">
         <v>280</v>
       </c>
-      <c r="Z19" s="23" t="n">
+      <c r="Z19" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA19" s="8" t="n">
@@ -5158,7 +5164,7 @@
           <t>NILTON J PEREIRA</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -5245,81 +5251,81 @@
           <t>SENARIA DO NASCIMENTO MALTA</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="C21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="23" t="n">
+      <c r="C21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="26" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="F21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="23" t="n">
+      <c r="F21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="I21" s="23" t="n">
+      <c r="I21" s="26" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="K21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="23" t="n">
+      <c r="K21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA21" s="8" t="n">
@@ -5332,7 +5338,7 @@
           <t>VINICIUS NICOLAS DE ALMEIDA</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -5349,7 +5355,7 @@
       <c r="F22" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="G22" s="23" t="n">
+      <c r="G22" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="6" t="n">
@@ -5361,13 +5367,13 @@
       <c r="J22" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="K22" s="23" t="n">
+      <c r="K22" s="26" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="M22" s="23" t="n">
+      <c r="M22" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="6" t="n">
@@ -5376,16 +5382,16 @@
       <c r="O22" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="P22" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="23" t="n">
+      <c r="P22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="26" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="S22" s="23" t="n">
+      <c r="S22" s="26" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="6" t="n">
@@ -5394,16 +5400,16 @@
       <c r="U22" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="V22" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="23" t="n">
+      <c r="V22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="26" t="n">
         <v>0</v>
       </c>
       <c r="Z22" s="6" t="n">
@@ -5419,7 +5425,7 @@
           <t>RACHEL DA CRUZ</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>23, 24</t>
         </is>
@@ -5493,7 +5499,7 @@
       <c r="Y23" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="Z23" s="23" t="n">
+      <c r="Z23" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="n">
@@ -5506,7 +5512,7 @@
           <t>LEANDRO A SILVA</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -5520,13 +5526,13 @@
       <c r="E24" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="F24" s="23" t="n">
+      <c r="F24" s="26" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="H24" s="23" t="n">
+      <c r="H24" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="6" t="n">
@@ -5553,34 +5559,34 @@
       <c r="P24" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="Q24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="23" t="n">
+      <c r="Q24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="n">
@@ -5593,7 +5599,7 @@
           <t>EDSON EMILIO DA COSTA</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -5680,81 +5686,81 @@
           <t>JOSE NAILTON LOPES DA SILVA</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
-        <is>
-          <t>28</t>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>28, 29</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="D26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="23" t="n">
+      <c r="D26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="26" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="H26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="23" t="n">
+      <c r="H26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" s="8" t="n">
@@ -5767,54 +5773,54 @@
           <t>GILBERTO MUNIN JUNIOR</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>28, 29</t>
         </is>
       </c>
-      <c r="C27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="23" t="n">
+      <c r="C27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="26" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="K27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="23" t="n">
+      <c r="K27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="26" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="N27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="23" t="n">
+      <c r="N27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="26" t="n">
         <v>0</v>
       </c>
       <c r="R27" s="6" t="n">
@@ -5823,25 +5829,25 @@
       <c r="S27" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="T27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="23" t="n">
+      <c r="T27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="26" t="n">
         <v>0</v>
       </c>
       <c r="V27" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="W27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="23" t="n">
+      <c r="W27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AA27" s="8" t="n">
@@ -5849,12 +5855,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n"/>
+      <c r="B29" s="18" t="n"/>
       <c r="C29" s="8" t="n">
         <v>10000</v>
       </c>
@@ -5927,7 +5933,7 @@
       <c r="Z29" s="8" t="n">
         <v>1250</v>
       </c>
-      <c r="AA29" s="17" t="n">
+      <c r="AA29" s="20" t="n">
         <v>112780</v>
       </c>
     </row>
@@ -5945,7 +5951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5956,41 +5962,41 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>SAÍDAS - PAGAMENTOS REALIZADOS</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Total de saídas: R$ 159,793.45</t>
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Total de saídas: R$ 55,211.92</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>DESTINATÁRIO</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>VALOR (R$)</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>CATEGORIA</t>
         </is>
@@ -5999,75 +6005,75 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>15/07/2024</t>
+          <t>23/07/2024</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>BOLETO</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Investimento automático</t>
+          <t>IBIUNA</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>8800</v>
+        <v>45.1</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>PREFEITURA/CARTÓRIO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>16/07/2024</t>
+          <t>23/07/2024</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>BOLETO</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Investimento automático</t>
+          <t>IBIUNA</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>500</v>
+        <v>45.1</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>PREFEITURA/CARTÓRIO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>21/07/2024</t>
+          <t>23/07/2024</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>BOLETO</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Investimento automático</t>
+          <t>IBIUNA</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1500</v>
+        <v>135.32</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>PREFEITURA/CARTÓRIO</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6119,7 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>45.1</v>
+        <v>135.32</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -6124,82 +6130,82 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>23/07/2024</t>
+          <t>24/07/2024</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>BOLETO</t>
+          <t>PIX ENVIADO</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>IBIUNA</t>
+          <t>Cesar Augusto de Oliveira</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>135.32</v>
+        <v>3000</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>PREFEITURA/CARTÓRIO</t>
+          <t>PIX P/ TERCEIROS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>23/07/2024</t>
+          <t>24/07/2024</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>BOLETO</t>
+          <t>PIX ENVIADO</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>IBIUNA</t>
+          <t>MARINA LEITE AGOSTINHO SOCIEDADE</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>45.1</v>
+        <v>6000</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>PREFEITURA/CARTÓRIO</t>
+          <t>HONORÁRIOS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>23/07/2024</t>
+          <t>27/08/2024</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>BOLETO</t>
+          <t>PIX ENVIADO</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>IBIUNA</t>
+          <t>Marina Leite Agostinho Sociedade Individual de</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>135.32</v>
+        <v>9000</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>PREFEITURA/CARTÓRIO</t>
+          <t>HONORÁRIOS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>24/07/2024</t>
+          <t>21/09/2024</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -6209,11 +6215,11 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Cesar Augusto de Oliveira</t>
+          <t>ALISSON RAFAEL MORAES</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>3000</v>
+        <v>35.36</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -6224,7 +6230,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>24/07/2024</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -6234,147 +6240,147 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>MARINA LEITE AGOSTINHO SOCIEDADE</t>
+          <t>Editora Ibiuna Ltda</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>6000</v>
+        <v>190</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>HONORÁRIOS</t>
+          <t>PREFEITURA/CARTÓRIO</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>06/08/2024</t>
+          <t>13/10/2024</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>PIX ENVIADO</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Investimento automático</t>
+          <t>WANIA CRISTINA DA CRUZ</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>594.16</v>
+        <v>138.69</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>PIX P/ TERCEIROS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>11/08/2024</t>
+          <t>23/10/2024</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>PIX ENVIADO</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Investimento automático</t>
+          <t>Dionisio Grangeiro Neto</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>6000</v>
+        <v>4950</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>TOPÓGRAFO</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>13/08/2024</t>
+          <t>17/01/2025</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>PIX ENVIADO</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Investimento automático</t>
+          <t>Dionisio Grangeiro Neto</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>500</v>
+        <v>11900</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>TOPÓGRAFO</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>18/08/2024</t>
+          <t>17/03/2025</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>PIX ENVIADO</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Investimento automático</t>
+          <t>DIONISIO GRANGEIRO NETO</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1000</v>
+        <v>11900</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>TOPÓGRAFO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>25/08/2024</t>
+          <t>22/04/2025</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>PIX ENVIADO</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Investimento automático</t>
+          <t>Gicele Capovilla Alves</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1500</v>
+        <v>3800</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>PIX P/ TERCEIROS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>27/08/2024</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -6384,47 +6390,47 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Marina Leite Agostinho Sociedade Individual de</t>
+          <t>JOSE OGIER JACOM NETO</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>9000</v>
+        <v>1750</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>HONORÁRIOS</t>
+          <t>PIX P/ TERCEIROS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>16/09/2024</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>PIX ENVIADO</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Investimento automático</t>
+          <t>SIMONE BASTOS GOMES</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6000</v>
+        <v>196.43</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>APLICAÇÃO RDB</t>
+          <t>PIX P/ TERCEIROS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>21/09/2024</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -6434,11 +6440,11 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>ALISSON RAFAEL MORAES</t>
+          <t>Simone Bastos Gomes</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>35.36</v>
+        <v>1750</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -6449,21 +6455,21 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>10/10/2024</t>
+          <t>09/02/2026</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>PIX ENVIADO</t>
+          <t>BOLETO</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Editora Ibiuna Ltda</t>
+          <t>GEAZI ASSIS DE SOUZA OLIVEIRA</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>190</v>
+        <v>195.5</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -6471,823 +6477,107 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>13/10/2024</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>PIX ENVIADO</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>WANIA CRISTINA DA CRUZ</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>138.69</v>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>PIX P/ TERCEIROS</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>13/10/2024</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>7635.95</v>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>23/10/2024</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>PIX ENVIADO</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Dionisio Grangeiro Neto</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="n">
-        <v>4950</v>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>TOPÓGRAFO</t>
-        </is>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>TOTAL GERAL</t>
+        </is>
+      </c>
+      <c r="D25" s="30" t="n">
+        <v>55211.92000000001</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>30/10/2024</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>500</v>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>RESUMO POR CATEGORIA</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>24/11/2024</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="n">
-        <v>7250</v>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>CATEGORIA</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL (R$)</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="n">
-        <v>7000</v>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
+          <t>HONORÁRIOS</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="33" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D29" s="34" t="n">
+        <v>0.2716804632043225</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>07/01/2025</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="n">
-        <v>250</v>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
+          <t>TOPÓGRAFO</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="33" t="n">
+        <v>28750</v>
+      </c>
+      <c r="D30" s="34" t="n">
+        <v>0.5207208878082848</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>12/01/2025</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
+          <t>PREFEITURA/CARTÓRIO</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" s="33" t="n">
+        <v>791.4400000000001</v>
+      </c>
+      <c r="D31" s="34" t="n">
+        <v>0.01433458571989527</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>17/01/2025</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>PIX ENVIADO</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Dionisio Grangeiro Neto</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="n">
-        <v>11900</v>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>TOPÓGRAFO</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>02/02/2025</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>23/02/2025</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>3250</v>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>16/03/2025</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="n">
-        <v>3250</v>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>17/03/2025</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>PIX ENVIADO</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>DIONISIO GRANGEIRO NETO</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="n">
-        <v>11900</v>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>TOPÓGRAFO</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>12/04/2025</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>2750</v>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>22/04/2025</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>PIX ENVIADO</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Gicele Capovilla Alves</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>3800</v>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
           <t>PIX P/ TERCEIROS</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>15/06/2025</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>10251.42</v>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>01/07/2025</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>PIX ENVIADO</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>JOSE OGIER JACOM NETO</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="n">
-        <v>1750</v>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>PIX P/ TERCEIROS</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>08/08/2025</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>3750</v>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>11/08/2025</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>2250</v>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>08/09/2025</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>12/10/2025</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>6500</v>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>06/11/2025</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>PIX ENVIADO</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>SIMONE BASTOS GOMES</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>196.43</v>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>PIX P/ TERCEIROS</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>10/11/2025</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>PIX ENVIADO</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Simone Bastos Gomes</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>1750</v>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>PIX P/ TERCEIROS</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>13/12/2025</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="n">
-        <v>5500</v>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>09/02/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>BOLETO</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>GEAZI ASSIS DE SOUZA OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="n">
-        <v>195.5</v>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>PREFEITURA/CARTÓRIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>16/03/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="n">
-        <v>9600</v>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="n">
-        <v>2700</v>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>Investimento automático</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" s="25" t="inlineStr">
-        <is>
-          <t>TOTAL GERAL</t>
-        </is>
-      </c>
-      <c r="D53" s="27" t="n">
-        <v>159793.45</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="28" t="inlineStr">
-        <is>
-          <t>RESUMO POR CATEGORIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="29" t="inlineStr">
-        <is>
-          <t>CATEGORIA</t>
-        </is>
-      </c>
-      <c r="B56" s="29" t="inlineStr">
-        <is>
-          <t>QTD</t>
-        </is>
-      </c>
-      <c r="C56" s="29" t="inlineStr">
-        <is>
-          <t>TOTAL (R$)</t>
-        </is>
-      </c>
-      <c r="D56" s="29" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>HONORÁRIOS</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C57" s="30" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D57" s="31" t="n">
-        <v>0.0938711818287921</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>TOPÓGRAFO</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C58" s="30" t="n">
-        <v>28750</v>
-      </c>
-      <c r="D58" s="31" t="n">
-        <v>0.1799197651718515</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>PREFEITURA/CARTÓRIO</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="n">
+      <c r="B32" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C59" s="30" t="n">
-        <v>791.4400000000001</v>
-      </c>
-      <c r="D59" s="31" t="n">
-        <v>0.004952893876438615</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>PIX P/ TERCEIROS</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C60" s="30" t="n">
+      <c r="C32" s="33" t="n">
         <v>10670.48</v>
       </c>
-      <c r="D60" s="31" t="n">
-        <v>0.06677670455203263</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO RDB</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="C61" s="30" t="n">
-        <v>104581.53</v>
-      </c>
-      <c r="D61" s="31" t="n">
-        <v>0.6544794545708851</v>
+      <c r="D32" s="34" t="n">
+        <v>0.1932640632674973</v>
       </c>
     </row>
   </sheetData>
@@ -7323,39 +6613,39 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
-        <is>
-          <t>Saldo inicial: R$ 0,10 | Saldo final: R$ 1.841,29</t>
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>Aplicações RDB excluídas conforme solicitação</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>MÊS</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>ENTRADAS</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>SAÍDAS (Pgtos)</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>SAÍDAS (RDB)</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t>TOTAL SAÍDAS</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="32" t="inlineStr">
         <is>
           <t>SALDO MENSAL</t>
         </is>
@@ -7367,20 +6657,20 @@
           <t>JUL/24</t>
         </is>
       </c>
-      <c r="B5" s="33" t="n">
+      <c r="B5" s="36" t="n">
         <v>10000</v>
       </c>
-      <c r="C5" s="34" t="n">
+      <c r="C5" s="37" t="n">
         <v>9405.940000000001</v>
       </c>
-      <c r="D5" s="35" t="n">
-        <v>10800</v>
-      </c>
-      <c r="E5" s="30" t="n">
-        <v>20205.94</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>-10205.94</v>
+      <c r="D5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>9405.940000000001</v>
+      </c>
+      <c r="F5" s="38" t="n">
+        <v>594.0599999999995</v>
       </c>
     </row>
     <row r="6">
@@ -7389,20 +6679,20 @@
           <t>AGO/24</t>
         </is>
       </c>
-      <c r="B6" s="33" t="n">
+      <c r="B6" s="36" t="n">
         <v>9500</v>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C6" s="37" t="n">
         <v>9000</v>
       </c>
-      <c r="D6" s="35" t="n">
-        <v>9594.16</v>
-      </c>
-      <c r="E6" s="30" t="n">
-        <v>18594.16</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>-9094.16</v>
+      <c r="D6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F6" s="38" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="7">
@@ -7411,20 +6701,20 @@
           <t>SET/24</t>
         </is>
       </c>
-      <c r="B7" s="33" t="n">
+      <c r="B7" s="36" t="n">
         <v>9500</v>
       </c>
-      <c r="C7" s="34" t="n">
+      <c r="C7" s="37" t="n">
         <v>35.36</v>
       </c>
-      <c r="D7" s="35" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E7" s="30" t="n">
-        <v>6035.36</v>
-      </c>
-      <c r="F7" s="36" t="n">
-        <v>3464.64</v>
+      <c r="D7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="F7" s="38" t="n">
+        <v>9464.639999999999</v>
       </c>
     </row>
     <row r="8">
@@ -7433,20 +6723,20 @@
           <t>OUT/24</t>
         </is>
       </c>
-      <c r="B8" s="33" t="n">
+      <c r="B8" s="36" t="n">
         <v>8500</v>
       </c>
-      <c r="C8" s="34" t="n">
+      <c r="C8" s="37" t="n">
         <v>5278.69</v>
       </c>
-      <c r="D8" s="35" t="n">
-        <v>8135.95</v>
-      </c>
-      <c r="E8" s="30" t="n">
-        <v>13414.64</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>-4914.639999999999</v>
+      <c r="D8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>5278.69</v>
+      </c>
+      <c r="F8" s="38" t="n">
+        <v>3221.31</v>
       </c>
     </row>
     <row r="9">
@@ -7455,20 +6745,20 @@
           <t>NOV/24</t>
         </is>
       </c>
-      <c r="B9" s="33" t="n">
+      <c r="B9" s="36" t="n">
         <v>8250</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="35" t="n">
-        <v>7250</v>
-      </c>
-      <c r="E9" s="30" t="n">
-        <v>7250</v>
-      </c>
-      <c r="F9" s="36" t="n">
-        <v>1000</v>
+      <c r="D9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="38" t="n">
+        <v>8250</v>
       </c>
     </row>
     <row r="10">
@@ -7477,7 +6767,7 @@
           <t>DEZ/24</t>
         </is>
       </c>
-      <c r="B10" s="33" t="n">
+      <c r="B10" s="36" t="n">
         <v>6000</v>
       </c>
       <c r="C10" s="9" t="n">
@@ -7486,10 +6776,10 @@
       <c r="D10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="36" t="n">
+      <c r="E10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="38" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -7499,20 +6789,20 @@
           <t>JAN/25</t>
         </is>
       </c>
-      <c r="B11" s="33" t="n">
+      <c r="B11" s="36" t="n">
         <v>3000</v>
       </c>
-      <c r="C11" s="34" t="n">
+      <c r="C11" s="37" t="n">
         <v>11900</v>
       </c>
-      <c r="D11" s="35" t="n">
-        <v>8500</v>
-      </c>
-      <c r="E11" s="30" t="n">
-        <v>20400</v>
+      <c r="D11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <v>11900</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>-17400</v>
+        <v>-8900</v>
       </c>
     </row>
     <row r="12">
@@ -7521,20 +6811,20 @@
           <t>FEV/25</t>
         </is>
       </c>
-      <c r="B12" s="33" t="n">
+      <c r="B12" s="36" t="n">
         <v>4250</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="35" t="n">
-        <v>4750</v>
-      </c>
-      <c r="E12" s="30" t="n">
-        <v>4750</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>-500</v>
+      <c r="D12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="38" t="n">
+        <v>4250</v>
       </c>
     </row>
     <row r="13">
@@ -7543,20 +6833,20 @@
           <t>MAR/25</t>
         </is>
       </c>
-      <c r="B13" s="33" t="n">
+      <c r="B13" s="36" t="n">
         <v>4000</v>
       </c>
-      <c r="C13" s="34" t="n">
+      <c r="C13" s="37" t="n">
         <v>11900</v>
       </c>
-      <c r="D13" s="35" t="n">
-        <v>3250</v>
-      </c>
-      <c r="E13" s="30" t="n">
-        <v>15150</v>
+      <c r="D13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>11900</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>-11150</v>
+        <v>-7900</v>
       </c>
     </row>
     <row r="14">
@@ -7565,20 +6855,20 @@
           <t>ABR/25</t>
         </is>
       </c>
-      <c r="B14" s="33" t="n">
+      <c r="B14" s="36" t="n">
         <v>4500</v>
       </c>
-      <c r="C14" s="34" t="n">
+      <c r="C14" s="37" t="n">
         <v>3800</v>
       </c>
-      <c r="D14" s="35" t="n">
-        <v>2750</v>
-      </c>
-      <c r="E14" s="30" t="n">
-        <v>6550</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>-2050</v>
+      <c r="D14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="33" t="n">
+        <v>3800</v>
+      </c>
+      <c r="F14" s="38" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="15">
@@ -7587,7 +6877,7 @@
           <t>MAI/25</t>
         </is>
       </c>
-      <c r="B15" s="33" t="n">
+      <c r="B15" s="36" t="n">
         <v>4500</v>
       </c>
       <c r="C15" s="9" t="n">
@@ -7596,10 +6886,10 @@
       <c r="D15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="36" t="n">
+      <c r="E15" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="38" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -7609,20 +6899,20 @@
           <t>JUN/25</t>
         </is>
       </c>
-      <c r="B16" s="33" t="n">
+      <c r="B16" s="36" t="n">
         <v>4000</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="35" t="n">
-        <v>10251.42</v>
-      </c>
-      <c r="E16" s="30" t="n">
-        <v>10251.42</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>-6251.42</v>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="38" t="n">
+        <v>4000</v>
       </c>
     </row>
     <row r="17">
@@ -7631,19 +6921,19 @@
           <t>JUL/25</t>
         </is>
       </c>
-      <c r="B17" s="33" t="n">
+      <c r="B17" s="36" t="n">
         <v>3500</v>
       </c>
-      <c r="C17" s="34" t="n">
+      <c r="C17" s="37" t="n">
         <v>1750</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="30" t="n">
+      <c r="E17" s="33" t="n">
         <v>1750</v>
       </c>
-      <c r="F17" s="36" t="n">
+      <c r="F17" s="38" t="n">
         <v>1750</v>
       </c>
     </row>
@@ -7653,20 +6943,20 @@
           <t>AGO/25</t>
         </is>
       </c>
-      <c r="B18" s="33" t="n">
+      <c r="B18" s="36" t="n">
         <v>3250</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="35" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E18" s="30" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>-2750</v>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="38" t="n">
+        <v>3250</v>
       </c>
     </row>
     <row r="19">
@@ -7675,20 +6965,20 @@
           <t>SET/25</t>
         </is>
       </c>
-      <c r="B19" s="33" t="n">
+      <c r="B19" s="36" t="n">
         <v>3250</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E19" s="30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F19" s="36" t="n">
-        <v>2250</v>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="38" t="n">
+        <v>3250</v>
       </c>
     </row>
     <row r="20">
@@ -7697,20 +6987,20 @@
           <t>OUT/25</t>
         </is>
       </c>
-      <c r="B20" s="33" t="n">
+      <c r="B20" s="36" t="n">
         <v>4250</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="35" t="n">
-        <v>6500</v>
-      </c>
-      <c r="E20" s="30" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>-2250</v>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="38" t="n">
+        <v>4250</v>
       </c>
     </row>
     <row r="21">
@@ -7719,19 +7009,19 @@
           <t>NOV/25</t>
         </is>
       </c>
-      <c r="B21" s="33" t="n">
+      <c r="B21" s="36" t="n">
         <v>4000</v>
       </c>
-      <c r="C21" s="34" t="n">
+      <c r="C21" s="37" t="n">
         <v>1946.43</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="30" t="n">
+      <c r="E21" s="33" t="n">
         <v>1946.43</v>
       </c>
-      <c r="F21" s="36" t="n">
+      <c r="F21" s="38" t="n">
         <v>2053.57</v>
       </c>
     </row>
@@ -7741,20 +7031,20 @@
           <t>DEZ/25</t>
         </is>
       </c>
-      <c r="B22" s="33" t="n">
+      <c r="B22" s="36" t="n">
         <v>3250</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="35" t="n">
-        <v>5500</v>
-      </c>
-      <c r="E22" s="30" t="n">
-        <v>5500</v>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>-2250</v>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="38" t="n">
+        <v>3250</v>
       </c>
     </row>
     <row r="23">
@@ -7763,7 +7053,7 @@
           <t>JAN/26</t>
         </is>
       </c>
-      <c r="B23" s="33" t="n">
+      <c r="B23" s="36" t="n">
         <v>2750</v>
       </c>
       <c r="C23" s="9" t="n">
@@ -7772,10 +7062,10 @@
       <c r="D23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="36" t="n">
+      <c r="E23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="38" t="n">
         <v>2750</v>
       </c>
     </row>
@@ -7785,19 +7075,19 @@
           <t>FEV/26</t>
         </is>
       </c>
-      <c r="B24" s="33" t="n">
+      <c r="B24" s="36" t="n">
         <v>3750</v>
       </c>
-      <c r="C24" s="34" t="n">
+      <c r="C24" s="37" t="n">
         <v>195.5</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="30" t="n">
+      <c r="E24" s="33" t="n">
         <v>195.5</v>
       </c>
-      <c r="F24" s="36" t="n">
+      <c r="F24" s="38" t="n">
         <v>3554.5</v>
       </c>
     </row>
@@ -7807,20 +7097,20 @@
           <t>MAR/26</t>
         </is>
       </c>
-      <c r="B25" s="33" t="n">
+      <c r="B25" s="36" t="n">
         <v>3000</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="35" t="n">
-        <v>9600</v>
-      </c>
-      <c r="E25" s="30" t="n">
-        <v>9600</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>-6600</v>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="38" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="26">
@@ -7829,20 +7119,20 @@
           <t>ABR/26</t>
         </is>
       </c>
-      <c r="B26" s="33" t="n">
+      <c r="B26" s="36" t="n">
         <v>2000</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="35" t="n">
-        <v>2700</v>
-      </c>
-      <c r="E26" s="30" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F26" s="10" t="n">
-        <v>-700</v>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="38" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="27">
@@ -7851,20 +7141,20 @@
           <t>MAI/26</t>
         </is>
       </c>
-      <c r="B27" s="33" t="n">
+      <c r="B27" s="36" t="n">
         <v>2530</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="35" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E27" s="30" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F27" s="36" t="n">
-        <v>530</v>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="38" t="n">
+        <v>2530</v>
       </c>
     </row>
     <row r="28">
@@ -7873,7 +7163,7 @@
           <t>JUN/26</t>
         </is>
       </c>
-      <c r="B28" s="33" t="n">
+      <c r="B28" s="36" t="n">
         <v>1250</v>
       </c>
       <c r="C28" s="9" t="n">
@@ -7882,33 +7172,33 @@
       <c r="D28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="36" t="n">
+      <c r="E28" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="38" t="n">
         <v>1250</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n">
+      <c r="B30" s="20" t="n">
         <v>112780</v>
       </c>
-      <c r="C30" s="17" t="n">
+      <c r="C30" s="20" t="n">
         <v>55211.92000000001</v>
       </c>
-      <c r="D30" s="17" t="n">
-        <v>104581.53</v>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>159793.45</v>
-      </c>
-      <c r="F30" s="17" t="n">
-        <v>-47013.45</v>
+      <c r="D30" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="20" t="n">
+        <v>55211.92000000001</v>
+      </c>
+      <c r="F30" s="20" t="n">
+        <v>57568.07999999999</v>
       </c>
     </row>
   </sheetData>
@@ -7943,27 +7233,27 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>PAGADOR</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>NOME NO EXTRATO</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>VALOR (R$)</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>LOTE(S)</t>
         </is>
@@ -8265,7 +7555,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -8365,7 +7655,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>28, 29</t>
         </is>
       </c>
     </row>
@@ -8465,7 +7755,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -8490,7 +7780,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8205,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -9940,7 +9230,7 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>28, 29</t>
         </is>
       </c>
     </row>
@@ -11090,7 +10380,7 @@
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -11390,7 +10680,7 @@
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -11690,7 +10980,7 @@
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -11915,7 +11205,7 @@
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -12140,7 +11430,7 @@
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -12415,7 +11705,7 @@
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -12715,7 +12005,7 @@
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -12965,7 +12255,7 @@
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -13140,7 +12430,7 @@
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -13440,7 +12730,7 @@
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -13665,7 +12955,7 @@
       </c>
       <c r="E231" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -13915,7 +13205,7 @@
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -14140,7 +13430,7 @@
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -14315,7 +13605,7 @@
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -14515,7 +13805,7 @@
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
-          <t>1, 2, 20, 29, 30</t>
+          <t>1, 2, 20, 30</t>
         </is>
       </c>
     </row>
@@ -14715,29 +14005,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>PONTOS DE ATENÇÃO E DIVERGÊNCIAS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>LOTE(S)</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>COMPRADOR</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
@@ -14759,7 +14049,7 @@
           <t>NUNCA PAGOU. R$ 0 de R$ 12.000.</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D4" s="40" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -14781,7 +14071,7 @@
           <t>Parou de pagar após NOV/2024. Saldo devedor alto.</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D5" s="40" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -14803,7 +14093,7 @@
           <t>Parou de pagar após OUT/2024.</t>
         </is>
       </c>
-      <c r="D6" s="38" t="inlineStr">
+      <c r="D6" s="40" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -14825,7 +14115,7 @@
           <t>Parou de pagar após MAR/2025.</t>
         </is>
       </c>
-      <c r="D7" s="38" t="inlineStr">
+      <c r="D7" s="40" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -14847,7 +14137,7 @@
           <t>Último pagamento JUN/2025.</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D8" s="40" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -14869,7 +14159,7 @@
           <t>Pagamentos irregulares. Último SET/2025.</t>
         </is>
       </c>
-      <c r="D9" s="38" t="inlineStr">
+      <c r="D9" s="40" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -14891,7 +14181,7 @@
           <t>Pagou apenas JUL/24. Eduardo N. Lobato continua pagando.</t>
         </is>
       </c>
-      <c r="D10" s="39" t="inlineStr">
+      <c r="D10" s="41" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -14905,7 +14195,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>GILBERTO MUNIN JUNIOR</t>
+          <t>GILBERTO MUNIN JUNIOR / JOSE NAILTON</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -14913,7 +14203,7 @@
           <t>Pagamentos irregulares (R$ 1.000 esporádicos). Sem pagto desde FEV/26.</t>
         </is>
       </c>
-      <c r="D11" s="39" t="inlineStr">
+      <c r="D11" s="41" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -14935,7 +14225,7 @@
           <t>Pagou R$ 30 em 26/05/2026 (habitual R$ 250). Verificar.</t>
         </is>
       </c>
-      <c r="D12" s="39" t="inlineStr">
+      <c r="D12" s="41" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -14944,7 +14234,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Lotes 1,2,20,29,30</t>
+          <t>Lotes 1,2,20,30</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -14957,7 +14247,7 @@
           <t>ABR/26: pagou R$ 500 (habitual R$ 750). Pagam pelos mesmos lotes.</t>
         </is>
       </c>
-      <c r="D13" s="39" t="inlineStr">
+      <c r="D13" s="41" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -14979,7 +14269,7 @@
           <t>Parcela reduzida. Pagou MAR/26 e parou.</t>
         </is>
       </c>
-      <c r="D14" s="39" t="inlineStr">
+      <c r="D14" s="41" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -15001,7 +14291,7 @@
           <t>Sem pagamento ABR/26 e JUN/26.</t>
         </is>
       </c>
-      <c r="D15" s="39" t="inlineStr">
+      <c r="D15" s="41" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -15023,7 +14313,7 @@
           <t>Pagamentos irregulares.</t>
         </is>
       </c>
-      <c r="D16" s="39" t="inlineStr">
+      <c r="D16" s="41" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -15045,7 +14335,7 @@
           <t>Consistente R$ 500/mês. Sem JUN/26 (extrato até 11/06).</t>
         </is>
       </c>
-      <c r="D17" s="40" t="inlineStr">
+      <c r="D17" s="42" t="inlineStr">
         <is>
           <t>OK</t>
         </is>

--- a/CONCILIACAO_COMPLETA_2024_2026.xlsx
+++ b/CONCILIACAO_COMPLETA_2024_2026.xlsx
@@ -13,6 +13,7 @@
     <sheet name="FLUXO DE CAIXA" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="DETALHE ENTRADAS" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="DIVERGÊNCIAS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CONCILIAÇÃO CAIXINHAS" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,8 +96,26 @@
       <b val="1"/>
       <color rgb="00FF0000"/>
     </font>
+    <font>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -145,6 +164,24 @@
         <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00548235"/>
+        <bgColor rgb="00548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -164,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -221,11 +258,33 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="13" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="16" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="17" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="18" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5951,7 +6010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5971,7 +6030,7 @@
     <row r="2">
       <c r="A2" s="28" t="inlineStr">
         <is>
-          <t>Total de saídas: R$ 55,211.92</t>
+          <t>Total de saídas: R$ 159,793.45</t>
         </is>
       </c>
     </row>
@@ -6005,75 +6064,75 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>23/07/2024</t>
+          <t>15/07/2024</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>BOLETO</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>IBIUNA</t>
+          <t>Investimento automático</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>45.1</v>
+        <v>8800</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>PREFEITURA/CARTÓRIO</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>23/07/2024</t>
+          <t>16/07/2024</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>BOLETO</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>IBIUNA</t>
+          <t>Investimento automático</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>45.1</v>
+        <v>500</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>PREFEITURA/CARTÓRIO</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>23/07/2024</t>
+          <t>21/07/2024</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>BOLETO</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>IBIUNA</t>
+          <t>Investimento automático</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>135.32</v>
+        <v>1500</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>PREFEITURA/CARTÓRIO</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6178,7 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>135.32</v>
+        <v>45.1</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -6130,82 +6189,82 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>24/07/2024</t>
+          <t>23/07/2024</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>PIX ENVIADO</t>
+          <t>BOLETO</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Cesar Augusto de Oliveira</t>
+          <t>IBIUNA</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>3000</v>
+        <v>135.32</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>PIX P/ TERCEIROS</t>
+          <t>PREFEITURA/CARTÓRIO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>24/07/2024</t>
+          <t>23/07/2024</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>PIX ENVIADO</t>
+          <t>BOLETO</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>MARINA LEITE AGOSTINHO SOCIEDADE</t>
+          <t>IBIUNA</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>6000</v>
+        <v>45.1</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>HONORÁRIOS</t>
+          <t>PREFEITURA/CARTÓRIO</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>27/08/2024</t>
+          <t>23/07/2024</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>PIX ENVIADO</t>
+          <t>BOLETO</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Marina Leite Agostinho Sociedade Individual de</t>
+          <t>IBIUNA</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>9000</v>
+        <v>135.32</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>HONORÁRIOS</t>
+          <t>PREFEITURA/CARTÓRIO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>21/09/2024</t>
+          <t>24/07/2024</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -6215,11 +6274,11 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>ALISSON RAFAEL MORAES</t>
+          <t>Cesar Augusto de Oliveira</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>35.36</v>
+        <v>3000</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -6230,7 +6289,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>10/10/2024</t>
+          <t>24/07/2024</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -6240,147 +6299,147 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Editora Ibiuna Ltda</t>
+          <t>MARINA LEITE AGOSTINHO SOCIEDADE</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>190</v>
+        <v>6000</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>PREFEITURA/CARTÓRIO</t>
+          <t>HONORÁRIOS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>13/10/2024</t>
+          <t>06/08/2024</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>PIX ENVIADO</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>WANIA CRISTINA DA CRUZ</t>
+          <t>Investimento automático</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>138.69</v>
+        <v>594.16</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>PIX P/ TERCEIROS</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>23/10/2024</t>
+          <t>11/08/2024</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>PIX ENVIADO</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Dionisio Grangeiro Neto</t>
+          <t>Investimento automático</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>4950</v>
+        <v>6000</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>TOPÓGRAFO</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>17/01/2025</t>
+          <t>13/08/2024</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>PIX ENVIADO</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Dionisio Grangeiro Neto</t>
+          <t>Investimento automático</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>11900</v>
+        <v>500</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>TOPÓGRAFO</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>17/03/2025</t>
+          <t>18/08/2024</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>PIX ENVIADO</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>DIONISIO GRANGEIRO NETO</t>
+          <t>Investimento automático</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>11900</v>
+        <v>1000</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>TOPÓGRAFO</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>22/04/2025</t>
+          <t>25/08/2024</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>PIX ENVIADO</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Gicele Capovilla Alves</t>
+          <t>Investimento automático</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>3800</v>
+        <v>1500</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>PIX P/ TERCEIROS</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>27/08/2024</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -6390,47 +6449,47 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>JOSE OGIER JACOM NETO</t>
+          <t>Marina Leite Agostinho Sociedade Individual de</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>1750</v>
+        <v>9000</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>PIX P/ TERCEIROS</t>
+          <t>HONORÁRIOS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>16/09/2024</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>PIX ENVIADO</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>SIMONE BASTOS GOMES</t>
+          <t>Investimento automático</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>196.43</v>
+        <v>6000</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>PIX P/ TERCEIROS</t>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>21/09/2024</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -6440,11 +6499,11 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Simone Bastos Gomes</t>
+          <t>ALISSON RAFAEL MORAES</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>1750</v>
+        <v>35.36</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -6455,21 +6514,21 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>BOLETO</t>
+          <t>PIX ENVIADO</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>GEAZI ASSIS DE SOUZA OLIVEIRA</t>
+          <t>Editora Ibiuna Ltda</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>195.5</v>
+        <v>190</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -6477,107 +6536,823 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>13/10/2024</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>WANIA CRISTINA DA CRUZ</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>138.69</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>PIX P/ TERCEIROS</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="C25" s="28" t="inlineStr">
-        <is>
-          <t>TOTAL GERAL</t>
-        </is>
-      </c>
-      <c r="D25" s="30" t="n">
-        <v>55211.92000000001</v>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>13/10/2024</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>7635.95</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>23/10/2024</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Dionisio Grangeiro Neto</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>4950</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>TOPÓGRAFO</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="inlineStr">
-        <is>
-          <t>RESUMO POR CATEGORIA</t>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>30/10/2024</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>CATEGORIA</t>
-        </is>
-      </c>
-      <c r="B28" s="32" t="inlineStr">
-        <is>
-          <t>QTD</t>
-        </is>
-      </c>
-      <c r="C28" s="32" t="inlineStr">
-        <is>
-          <t>TOTAL (R$)</t>
-        </is>
-      </c>
-      <c r="D28" s="32" t="inlineStr">
-        <is>
-          <t>%</t>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>24/11/2024</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>HONORÁRIOS</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C29" s="33" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D29" s="34" t="n">
-        <v>0.2716804632043225</v>
+          <t>06/01/2025</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>TOPÓGRAFO</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C30" s="33" t="n">
-        <v>28750</v>
-      </c>
-      <c r="D30" s="34" t="n">
-        <v>0.5207208878082848</v>
+          <t>07/01/2025</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>250</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>PREFEITURA/CARTÓRIO</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C31" s="33" t="n">
-        <v>791.4400000000001</v>
-      </c>
-      <c r="D31" s="34" t="n">
-        <v>0.01433458571989527</v>
+          <t>12/01/2025</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>17/01/2025</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Dionisio Grangeiro Neto</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>11900</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>TOPÓGRAFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>23/02/2025</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>3250</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>16/03/2025</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>3250</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>17/03/2025</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>DIONISIO GRANGEIRO NETO</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>11900</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>TOPÓGRAFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>12/04/2025</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>22/04/2025</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Gicele Capovilla Alves</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
           <t>PIX P/ TERCEIROS</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2025</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>10251.42</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>JOSE OGIER JACOM NETO</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>1750</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>PIX P/ TERCEIROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>12/10/2025</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>06/11/2025</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>SIMONE BASTOS GOMES</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>196.43</v>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>PIX P/ TERCEIROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Simone Bastos Gomes</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>1750</v>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>PIX P/ TERCEIROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>13/12/2025</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>BOLETO</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>GEAZI ASSIS DE SOUZA OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>PREFEITURA/CARTÓRIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>9600</v>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Investimento automático</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" s="28" t="inlineStr">
+        <is>
+          <t>TOTAL GERAL</t>
+        </is>
+      </c>
+      <c r="D53" s="30" t="n">
+        <v>159793.45</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="31" t="inlineStr">
+        <is>
+          <t>RESUMO POR CATEGORIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="32" t="inlineStr">
+        <is>
+          <t>CATEGORIA</t>
+        </is>
+      </c>
+      <c r="B56" s="32" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
+      <c r="C56" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL (R$)</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>HONORÁRIOS</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" s="33" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D57" s="34" t="n">
+        <v>0.0938711818287921</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>TOPÓGRAFO</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" s="33" t="n">
+        <v>28750</v>
+      </c>
+      <c r="D58" s="34" t="n">
+        <v>0.1799197651718515</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>PREFEITURA/CARTÓRIO</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C32" s="33" t="n">
+      <c r="C59" s="33" t="n">
+        <v>791.4400000000001</v>
+      </c>
+      <c r="D59" s="34" t="n">
+        <v>0.004952893876438615</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>PIX P/ TERCEIROS</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C60" s="33" t="n">
         <v>10670.48</v>
       </c>
-      <c r="D32" s="34" t="n">
-        <v>0.1932640632674973</v>
+      <c r="D60" s="34" t="n">
+        <v>0.06677670455203263</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO RDB</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C61" s="33" t="n">
+        <v>104581.53</v>
+      </c>
+      <c r="D61" s="34" t="n">
+        <v>0.6544794545708851</v>
       </c>
     </row>
   </sheetData>
@@ -6615,7 +7390,7 @@
     <row r="2">
       <c r="A2" s="35" t="inlineStr">
         <is>
-          <t>Aplicações RDB excluídas conforme solicitação</t>
+          <t>Inclui aplicações RDB e pagamentos</t>
         </is>
       </c>
     </row>
@@ -6663,14 +7438,14 @@
       <c r="C5" s="37" t="n">
         <v>9405.940000000001</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>0</v>
+      <c r="D5" s="38" t="n">
+        <v>10800</v>
       </c>
       <c r="E5" s="33" t="n">
-        <v>9405.940000000001</v>
-      </c>
-      <c r="F5" s="38" t="n">
-        <v>594.0599999999995</v>
+        <v>20205.94</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>-10205.94</v>
       </c>
     </row>
     <row r="6">
@@ -6685,14 +7460,14 @@
       <c r="C6" s="37" t="n">
         <v>9000</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>0</v>
+      <c r="D6" s="38" t="n">
+        <v>9594.16</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>9000</v>
-      </c>
-      <c r="F6" s="38" t="n">
-        <v>500</v>
+        <v>18594.16</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>-9094.16</v>
       </c>
     </row>
     <row r="7">
@@ -6707,14 +7482,14 @@
       <c r="C7" s="37" t="n">
         <v>35.36</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>0</v>
+      <c r="D7" s="38" t="n">
+        <v>6000</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>35.36</v>
-      </c>
-      <c r="F7" s="38" t="n">
-        <v>9464.639999999999</v>
+        <v>6035.36</v>
+      </c>
+      <c r="F7" s="39" t="n">
+        <v>3464.64</v>
       </c>
     </row>
     <row r="8">
@@ -6729,14 +7504,14 @@
       <c r="C8" s="37" t="n">
         <v>5278.69</v>
       </c>
-      <c r="D8" s="9" t="n">
-        <v>0</v>
+      <c r="D8" s="38" t="n">
+        <v>8135.95</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>5278.69</v>
-      </c>
-      <c r="F8" s="38" t="n">
-        <v>3221.31</v>
+        <v>13414.64</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>-4914.639999999999</v>
       </c>
     </row>
     <row r="9">
@@ -6751,14 +7526,14 @@
       <c r="C9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>0</v>
+      <c r="D9" s="38" t="n">
+        <v>7250</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="38" t="n">
-        <v>8250</v>
+        <v>7250</v>
+      </c>
+      <c r="F9" s="39" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -6779,7 +7554,7 @@
       <c r="E10" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="38" t="n">
+      <c r="F10" s="39" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -6795,14 +7570,14 @@
       <c r="C11" s="37" t="n">
         <v>11900</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>0</v>
+      <c r="D11" s="38" t="n">
+        <v>8500</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>11900</v>
+        <v>20400</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>-8900</v>
+        <v>-17400</v>
       </c>
     </row>
     <row r="12">
@@ -6817,14 +7592,14 @@
       <c r="C12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="9" t="n">
-        <v>0</v>
+      <c r="D12" s="38" t="n">
+        <v>4750</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="38" t="n">
-        <v>4250</v>
+        <v>4750</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>-500</v>
       </c>
     </row>
     <row r="13">
@@ -6839,14 +7614,14 @@
       <c r="C13" s="37" t="n">
         <v>11900</v>
       </c>
-      <c r="D13" s="9" t="n">
-        <v>0</v>
+      <c r="D13" s="38" t="n">
+        <v>3250</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>11900</v>
+        <v>15150</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>-7900</v>
+        <v>-11150</v>
       </c>
     </row>
     <row r="14">
@@ -6861,14 +7636,14 @@
       <c r="C14" s="37" t="n">
         <v>3800</v>
       </c>
-      <c r="D14" s="9" t="n">
-        <v>0</v>
+      <c r="D14" s="38" t="n">
+        <v>2750</v>
       </c>
       <c r="E14" s="33" t="n">
-        <v>3800</v>
-      </c>
-      <c r="F14" s="38" t="n">
-        <v>700</v>
+        <v>6550</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>-2050</v>
       </c>
     </row>
     <row r="15">
@@ -6889,7 +7664,7 @@
       <c r="E15" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="38" t="n">
+      <c r="F15" s="39" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -6905,14 +7680,14 @@
       <c r="C16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="9" t="n">
-        <v>0</v>
+      <c r="D16" s="38" t="n">
+        <v>10251.42</v>
       </c>
       <c r="E16" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="38" t="n">
-        <v>4000</v>
+        <v>10251.42</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>-6251.42</v>
       </c>
     </row>
     <row r="17">
@@ -6933,7 +7708,7 @@
       <c r="E17" s="33" t="n">
         <v>1750</v>
       </c>
-      <c r="F17" s="38" t="n">
+      <c r="F17" s="39" t="n">
         <v>1750</v>
       </c>
     </row>
@@ -6949,14 +7724,14 @@
       <c r="C18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="9" t="n">
-        <v>0</v>
+      <c r="D18" s="38" t="n">
+        <v>6000</v>
       </c>
       <c r="E18" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="38" t="n">
-        <v>3250</v>
+        <v>6000</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>-2750</v>
       </c>
     </row>
     <row r="19">
@@ -6971,14 +7746,14 @@
       <c r="C19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="9" t="n">
-        <v>0</v>
+      <c r="D19" s="38" t="n">
+        <v>1000</v>
       </c>
       <c r="E19" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="38" t="n">
-        <v>3250</v>
+        <v>1000</v>
+      </c>
+      <c r="F19" s="39" t="n">
+        <v>2250</v>
       </c>
     </row>
     <row r="20">
@@ -6993,14 +7768,14 @@
       <c r="C20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="9" t="n">
-        <v>0</v>
+      <c r="D20" s="38" t="n">
+        <v>6500</v>
       </c>
       <c r="E20" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="38" t="n">
-        <v>4250</v>
+        <v>6500</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>-2250</v>
       </c>
     </row>
     <row r="21">
@@ -7021,7 +7796,7 @@
       <c r="E21" s="33" t="n">
         <v>1946.43</v>
       </c>
-      <c r="F21" s="38" t="n">
+      <c r="F21" s="39" t="n">
         <v>2053.57</v>
       </c>
     </row>
@@ -7037,14 +7812,14 @@
       <c r="C22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="9" t="n">
-        <v>0</v>
+      <c r="D22" s="38" t="n">
+        <v>5500</v>
       </c>
       <c r="E22" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="38" t="n">
-        <v>3250</v>
+        <v>5500</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>-2250</v>
       </c>
     </row>
     <row r="23">
@@ -7065,7 +7840,7 @@
       <c r="E23" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="38" t="n">
+      <c r="F23" s="39" t="n">
         <v>2750</v>
       </c>
     </row>
@@ -7087,7 +7862,7 @@
       <c r="E24" s="33" t="n">
         <v>195.5</v>
       </c>
-      <c r="F24" s="38" t="n">
+      <c r="F24" s="39" t="n">
         <v>3554.5</v>
       </c>
     </row>
@@ -7103,14 +7878,14 @@
       <c r="C25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="9" t="n">
-        <v>0</v>
+      <c r="D25" s="38" t="n">
+        <v>9600</v>
       </c>
       <c r="E25" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="38" t="n">
-        <v>3000</v>
+        <v>9600</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>-6600</v>
       </c>
     </row>
     <row r="26">
@@ -7125,14 +7900,14 @@
       <c r="C26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="9" t="n">
-        <v>0</v>
+      <c r="D26" s="38" t="n">
+        <v>2700</v>
       </c>
       <c r="E26" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="38" t="n">
-        <v>2000</v>
+        <v>2700</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>-700</v>
       </c>
     </row>
     <row r="27">
@@ -7147,14 +7922,14 @@
       <c r="C27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="9" t="n">
-        <v>0</v>
+      <c r="D27" s="38" t="n">
+        <v>2000</v>
       </c>
       <c r="E27" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="38" t="n">
-        <v>2530</v>
+        <v>2000</v>
+      </c>
+      <c r="F27" s="39" t="n">
+        <v>530</v>
       </c>
     </row>
     <row r="28">
@@ -7175,7 +7950,7 @@
       <c r="E28" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="38" t="n">
+      <c r="F28" s="39" t="n">
         <v>1250</v>
       </c>
     </row>
@@ -7192,13 +7967,13 @@
         <v>55211.92000000001</v>
       </c>
       <c r="D30" s="20" t="n">
-        <v>0</v>
+        <v>104581.53</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>55211.92000000001</v>
+        <v>159793.45</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>57568.07999999999</v>
+        <v>-47013.45</v>
       </c>
     </row>
   </sheetData>
@@ -14005,7 +14780,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="39" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>PONTOS DE ATENÇÃO E DIVERGÊNCIAS</t>
         </is>
@@ -14049,7 +14824,7 @@
           <t>NUNCA PAGOU. R$ 0 de R$ 12.000.</t>
         </is>
       </c>
-      <c r="D4" s="40" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -14071,7 +14846,7 @@
           <t>Parou de pagar após NOV/2024. Saldo devedor alto.</t>
         </is>
       </c>
-      <c r="D5" s="40" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -14093,7 +14868,7 @@
           <t>Parou de pagar após OUT/2024.</t>
         </is>
       </c>
-      <c r="D6" s="40" t="inlineStr">
+      <c r="D6" s="41" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -14115,7 +14890,7 @@
           <t>Parou de pagar após MAR/2025.</t>
         </is>
       </c>
-      <c r="D7" s="40" t="inlineStr">
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -14137,7 +14912,7 @@
           <t>Último pagamento JUN/2025.</t>
         </is>
       </c>
-      <c r="D8" s="40" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -14159,7 +14934,7 @@
           <t>Pagamentos irregulares. Último SET/2025.</t>
         </is>
       </c>
-      <c r="D9" s="40" t="inlineStr">
+      <c r="D9" s="41" t="inlineStr">
         <is>
           <t>INADIMPLENTE</t>
         </is>
@@ -14181,7 +14956,7 @@
           <t>Pagou apenas JUL/24. Eduardo N. Lobato continua pagando.</t>
         </is>
       </c>
-      <c r="D10" s="41" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -14203,7 +14978,7 @@
           <t>Pagamentos irregulares (R$ 1.000 esporádicos). Sem pagto desde FEV/26.</t>
         </is>
       </c>
-      <c r="D11" s="41" t="inlineStr">
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -14225,7 +15000,7 @@
           <t>Pagou R$ 30 em 26/05/2026 (habitual R$ 250). Verificar.</t>
         </is>
       </c>
-      <c r="D12" s="41" t="inlineStr">
+      <c r="D12" s="42" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -14247,7 +15022,7 @@
           <t>ABR/26: pagou R$ 500 (habitual R$ 750). Pagam pelos mesmos lotes.</t>
         </is>
       </c>
-      <c r="D13" s="41" t="inlineStr">
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -14269,7 +15044,7 @@
           <t>Parcela reduzida. Pagou MAR/26 e parou.</t>
         </is>
       </c>
-      <c r="D14" s="41" t="inlineStr">
+      <c r="D14" s="42" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -14291,7 +15066,7 @@
           <t>Sem pagamento ABR/26 e JUN/26.</t>
         </is>
       </c>
-      <c r="D15" s="41" t="inlineStr">
+      <c r="D15" s="42" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -14313,7 +15088,7 @@
           <t>Pagamentos irregulares.</t>
         </is>
       </c>
-      <c r="D16" s="41" t="inlineStr">
+      <c r="D16" s="42" t="inlineStr">
         <is>
           <t>ATENÇÃO</t>
         </is>
@@ -14335,7 +15110,7 @@
           <t>Consistente R$ 500/mês. Sem JUN/26 (extrato até 11/06).</t>
         </is>
       </c>
-      <c r="D17" s="42" t="inlineStr">
+      <c r="D17" s="43" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -14344,4 +15119,1384 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CONCILIAÇÃO - EXTRATO CAIXINHAS RDB vs EXTRATO BANCÁRIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Período: MAI/2025 a JUN/2026 | Nu Financeira S.A. | Saldo final: R$ 68.284,51</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="45" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="B4" s="45" t="inlineStr">
+        <is>
+          <t>MOVIMENTAÇÃO</t>
+        </is>
+      </c>
+      <c r="C4" s="45" t="inlineStr">
+        <is>
+          <t>RENDIMENTO (R$)</t>
+        </is>
+      </c>
+      <c r="D4" s="45" t="inlineStr">
+        <is>
+          <t>VALOR APLICADO (R$)</t>
+        </is>
+      </c>
+      <c r="E4" s="45" t="inlineStr">
+        <is>
+          <t>SALDO ACUMULADO (R$)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>31/05/2025</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Rendimento</t>
+        </is>
+      </c>
+      <c r="C5" s="46" t="n">
+        <v>247.14</v>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="33" t="n">
+        <v>247.14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2025</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Compra por aplicação</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="46" t="n">
+        <v>10251.42</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>10498.56</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>30/06/2025</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Rendimento</t>
+        </is>
+      </c>
+      <c r="C7" s="46" t="n">
+        <v>205.7</v>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="33" t="n">
+        <v>10704.26</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Resgate</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>9704.26</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>31/07/2025</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Rendimento</t>
+        </is>
+      </c>
+      <c r="C9" s="46" t="n">
+        <v>418.99</v>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="33" t="n">
+        <v>10123.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Compra por aplicação</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="46" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>13873.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Compra por aplicação</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="46" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <v>16123.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>31/08/2025</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Rendimento</t>
+        </is>
+      </c>
+      <c r="C12" s="46" t="n">
+        <v>361.46</v>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="33" t="n">
+        <v>16484.71</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Compra por aplicação</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>17484.71</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Rendimento</t>
+        </is>
+      </c>
+      <c r="C14" s="46" t="n">
+        <v>471.49</v>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="33" t="n">
+        <v>17956.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Compra por aplicação</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="46" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E15" s="33" t="n">
+        <v>24456.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Rendimento</t>
+        </is>
+      </c>
+      <c r="C16" s="46" t="n">
+        <v>486.89</v>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="33" t="n">
+        <v>24943.09</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Resgate</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="47" t="n">
+        <v>500</v>
+      </c>
+      <c r="E17" s="33" t="n">
+        <v>24443.09</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>30/11/2025</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Rendimento</t>
+        </is>
+      </c>
+      <c r="C18" s="46" t="n">
+        <v>534.14</v>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="33" t="n">
+        <v>24977.23</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>13/12/2025</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Compra por aplicação</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="46" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E19" s="33" t="n">
+        <v>30477.23</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>31/12/2025</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Rendimento</t>
+        </is>
+      </c>
+      <c r="C20" s="46" t="n">
+        <v>517.86</v>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="33" t="n">
+        <v>30995.09</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>31/01/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Rendimento</t>
+        </is>
+      </c>
+      <c r="C21" s="46" t="n">
+        <v>649.9400000000001</v>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="33" t="n">
+        <v>31645.03</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>28/02/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Rendimento</t>
+        </is>
+      </c>
+      <c r="C22" s="46" t="n">
+        <v>509.98</v>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="33" t="n">
+        <v>32155.01</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Compra por aplicação</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="46" t="n">
+        <v>9600</v>
+      </c>
+      <c r="E23" s="33" t="n">
+        <v>41755.01</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Rendimento</t>
+        </is>
+      </c>
+      <c r="C24" s="46" t="n">
+        <v>597.8</v>
+      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="33" t="n">
+        <v>42352.81</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Compra por aplicação</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="46" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E25" s="33" t="n">
+        <v>45052.81</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Rendimento</t>
+        </is>
+      </c>
+      <c r="C26" s="46" t="n">
+        <v>733.22</v>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="33" t="n">
+        <v>45786.03</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Compra por aplicação</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="46" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E27" s="33" t="n">
+        <v>47786.03</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Rendimento</t>
+        </is>
+      </c>
+      <c r="C28" s="46" t="n">
+        <v>744.97</v>
+      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="33" t="n">
+        <v>48531</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Rendimento</t>
+        </is>
+      </c>
+      <c r="C29" s="46" t="n">
+        <v>247.26</v>
+      </c>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="33" t="n">
+        <v>48778.26</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>TOTAIS</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="48" t="n">
+        <v>6726.84</v>
+      </c>
+      <c r="D31" s="48" t="n">
+        <v>43551.42</v>
+      </c>
+      <c r="E31" s="49" t="n">
+        <v>48778.26</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>RESUMO CAIXINHAS RDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="50" t="inlineStr">
+        <is>
+          <t>Total aplicado (compras)</t>
+        </is>
+      </c>
+      <c r="B34" s="51" t="n">
+        <v>43551.42</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="50" t="inlineStr">
+        <is>
+          <t>Total resgatado</t>
+        </is>
+      </c>
+      <c r="B35" s="51" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="50" t="inlineStr">
+        <is>
+          <t>Total rendimentos</t>
+        </is>
+      </c>
+      <c r="B36" s="51" t="n">
+        <v>6726.840000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="50" t="inlineStr">
+        <is>
+          <t>Saldo final caixinhas (extrato)</t>
+        </is>
+      </c>
+      <c r="B37" s="51" t="n">
+        <v>68284.50999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="50" t="inlineStr">
+        <is>
+          <t>Saldo calculado</t>
+        </is>
+      </c>
+      <c r="B38" s="51" t="n">
+        <v>48778.26</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="50" t="inlineStr">
+        <is>
+          <t>Diferença</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n">
+        <v>19506.25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="53" t="inlineStr">
+        <is>
+          <t>CONCILIAÇÃO: EXTRATO BANCÁRIO vs CAIXINHAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Verifica se cada "Aplicação RDB" do extrato bancário bate com "Compra por aplicação" do extrato de caixinhas</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="54" t="inlineStr">
+        <is>
+          <t>DATA EXTRATO BANCÁRIO</t>
+        </is>
+      </c>
+      <c r="B44" s="54" t="inlineStr">
+        <is>
+          <t>VALOR EXTRATO (R$)</t>
+        </is>
+      </c>
+      <c r="C44" s="54" t="inlineStr">
+        <is>
+          <t>DATA CAIXINHAS</t>
+        </is>
+      </c>
+      <c r="D44" s="54" t="inlineStr">
+        <is>
+          <t>VALOR CAIXINHAS (R$)</t>
+        </is>
+      </c>
+      <c r="E44" s="54" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>15/07/2024</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>8800</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>16/07/2024</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>21/07/2024</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>06/08/2024</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="n">
+        <v>594.16</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>11/08/2024</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>13/08/2024</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>18/08/2024</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E51" s="56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>25/08/2024</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>16/09/2024</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E53" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>13/10/2024</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="n">
+        <v>7635.95</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E54" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>30/10/2024</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>24/11/2024</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="n">
+        <v>7250</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>06/01/2025</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E57" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>07/01/2025</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="n">
+        <v>250</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>12/01/2025</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E59" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E60" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>23/02/2025</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="n">
+        <v>3250</v>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>16/03/2025</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="n">
+        <v>3250</v>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E62" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>12/04/2025</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E63" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2025</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="n">
+        <v>10251.42</v>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2025</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>10251.42</v>
+      </c>
+      <c r="E64" s="56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>3750</v>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E65" s="56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E66" s="56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E67" s="55" t="inlineStr">
+        <is>
+          <t>NÃO ENCONTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>12/10/2025</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E68" s="56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>13/12/2025</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>13/12/2025</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E69" s="56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="n">
+        <v>9600</v>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>9600</v>
+      </c>
+      <c r="E70" s="56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="n">
+        <v>2700</v>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E71" s="56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E72" s="56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="57" t="inlineStr">
+        <is>
+          <t>TOTAL EXTRATO BANCÁRIO</t>
+        </is>
+      </c>
+      <c r="B74" s="48" t="n">
+        <v>104581.53</v>
+      </c>
+      <c r="C74" s="57" t="inlineStr">
+        <is>
+          <t>TOTAL CAIXINHAS</t>
+        </is>
+      </c>
+      <c r="D74" s="48" t="n">
+        <v>43551.42</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="58" t="inlineStr">
+        <is>
+          <t>DIFERENÇA</t>
+        </is>
+      </c>
+      <c r="B75" s="59" t="n">
+        <v>61030.11</v>
+      </c>
+      <c r="C75" s="60" t="inlineStr">
+        <is>
+          <t>DIVERGÊNCIA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>